--- a/final_combined_2methods_wide_ff.xlsx
+++ b/final_combined_2methods_wide_ff.xlsx
@@ -5,19 +5,21 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/JohnMatthew/Downloads/Thorne_15/FaIR_fut/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/JohnMatthew/Downloads/Thorne_15_codefigurestats/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0BB3260A-2D9E-9D4D-899C-E61AD7F6BC83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62124667-4D56-AA4D-9940-B2FE76A94E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7580" yWindow="5220" windowWidth="26840" windowHeight="15940" xr2:uid="{C5EFB806-CC49-FF45-A9BF-684F2EA9307C}"/>
+    <workbookView xWindow="4780" yWindow="500" windowWidth="31060" windowHeight="20320" activeTab="1" xr2:uid="{C5EFB806-CC49-FF45-A9BF-684F2EA9307C}"/>
   </bookViews>
   <sheets>
     <sheet name="final_combined_2methods_wide_ff" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId2"/>
     <externalReference r:id="rId3"/>
+    <externalReference r:id="rId4"/>
+    <externalReference r:id="rId5"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="38">
   <si>
     <t>experiment</t>
   </si>
@@ -134,17 +136,36 @@
   <si>
     <t>RMSE</t>
   </si>
+  <si>
+    <t>Compressed Mixture (CSCM), 7 methods</t>
+  </si>
+  <si>
+    <t>Compressed Mixture (CSCM), 18 methods</t>
+  </si>
+  <si>
+    <t>Inverse Variance (PIVW), 18 methods</t>
+  </si>
+  <si>
+    <t>Inverse Variance (PIVW), 7 methods</t>
+  </si>
+  <si>
+    <t>Compressed Mixture (CSCM), 37 methods</t>
+  </si>
+  <si>
+    <t>Inverse Variance (PIVW), 37 methods</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -278,6 +299,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="33">
@@ -577,7 +604,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="43">
+  <cellStyleXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -621,8 +648,9 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -630,8 +658,13 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="43" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="43">
+  <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="20" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="24" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="28" builtinId="38" customBuiltin="1"/>
@@ -659,6 +692,7 @@
     <cellStyle name="Bad" xfId="8" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Calculation" xfId="12" builtinId="22" customBuiltin="1"/>
     <cellStyle name="Check Cell" xfId="14" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Comma" xfId="43" builtinId="3"/>
     <cellStyle name="Explanatory Text" xfId="17" builtinId="53" customBuiltin="1"/>
     <cellStyle name="Good" xfId="7" builtinId="26" customBuiltin="1"/>
     <cellStyle name="Heading 1" xfId="3" builtinId="16" customBuiltin="1"/>
@@ -696,7 +730,7 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="final_combined_16methods_wide_f"/>
+      <sheetName val="final_combined_7methods_wide_ff"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
@@ -705,28 +739,57 @@
             <v>fut_ESM1-2-LR_SSP126_constVolc</v>
           </cell>
           <cell r="C2">
-            <v>0.23423231205582501</v>
+            <v>0.21132096210941201</v>
           </cell>
           <cell r="D2">
-            <v>0.44301513220746003</v>
+            <v>0.39883056449283</v>
           </cell>
           <cell r="E2">
-            <v>0.80477747916472697</v>
+            <v>0.74598077875606195</v>
           </cell>
           <cell r="F2">
-            <v>0.46624181380279101</v>
+            <v>0.528912270279561</v>
           </cell>
           <cell r="G2">
-            <v>0.49304442107483998</v>
+            <v>0.577668141911305</v>
           </cell>
           <cell r="H2">
-            <v>1.22</v>
+            <v>1.42</v>
           </cell>
           <cell r="I2">
-            <v>3.4209966316283001E-2</v>
+            <v>3.8089126961787199E-2</v>
           </cell>
           <cell r="J2">
-            <v>3.3170670153985497E-2</v>
+            <v>3.8257160319207201E-2</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3" t="str">
+            <v>fut_ESM1-2-LR_SSP126_constVolc</v>
+          </cell>
+          <cell r="C3">
+            <v>0.20755706849306199</v>
+          </cell>
+          <cell r="D3">
+            <v>0.39313285295950501</v>
+          </cell>
+          <cell r="E3">
+            <v>0.75508045533102697</v>
+          </cell>
+          <cell r="F3">
+            <v>0.56758655826126803</v>
+          </cell>
+          <cell r="G3">
+            <v>0.60241889512051305</v>
+          </cell>
+          <cell r="H3">
+            <v>1.46</v>
+          </cell>
+          <cell r="I3">
+            <v>3.55967136847853E-2</v>
+          </cell>
+          <cell r="J3">
+            <v>3.4755163366221101E-2</v>
           </cell>
         </row>
         <row r="4">
@@ -734,28 +797,57 @@
             <v>fut_ESM1-2-LR_SSP245_constVolc</v>
           </cell>
           <cell r="C4">
-            <v>0.54526216461403398</v>
+            <v>0.51324464439026996</v>
           </cell>
           <cell r="D4">
-            <v>0.85151612528392695</v>
+            <v>0.80791569847865796</v>
           </cell>
           <cell r="E4">
-            <v>0.98769878415374102</v>
+            <v>0.98599074521400898</v>
           </cell>
           <cell r="F4">
-            <v>0.34391488294497302</v>
+            <v>0.40375019023063502</v>
           </cell>
           <cell r="G4">
-            <v>0.33005863001684399</v>
+            <v>0.409028023352207</v>
           </cell>
           <cell r="H4">
-            <v>1.02</v>
+            <v>1.04</v>
           </cell>
           <cell r="I4">
-            <v>3.1604406760897701E-2</v>
+            <v>3.5707271533879398E-2</v>
           </cell>
           <cell r="J4">
-            <v>2.94731342330086E-2</v>
+            <v>3.4964253761786197E-2</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5" t="str">
+            <v>fut_ESM1-2-LR_SSP245_constVolc</v>
+          </cell>
+          <cell r="C5">
+            <v>0.55693243562445705</v>
+          </cell>
+          <cell r="D5">
+            <v>0.85137216343120803</v>
+          </cell>
+          <cell r="E5">
+            <v>0.99159617730083804</v>
+          </cell>
+          <cell r="F5">
+            <v>0.48770586775952401</v>
+          </cell>
+          <cell r="G5">
+            <v>0.48135376341167602</v>
+          </cell>
+          <cell r="H5">
+            <v>1.04</v>
+          </cell>
+          <cell r="I5">
+            <v>3.2207269952229799E-2</v>
+          </cell>
+          <cell r="J5">
+            <v>3.0085110989888701E-2</v>
           </cell>
         </row>
         <row r="6">
@@ -763,28 +855,57 @@
             <v>fut_ESM1-2-LR_SSP370_constVolc</v>
           </cell>
           <cell r="C6">
-            <v>0.58820103523420497</v>
+            <v>0.56326546202472005</v>
           </cell>
           <cell r="D6">
-            <v>0.882503084666731</v>
+            <v>0.85916848777764898</v>
           </cell>
           <cell r="E6">
-            <v>0.99999998110849297</v>
+            <v>0.99999972101326395</v>
           </cell>
           <cell r="F6">
-            <v>0.25605969664375</v>
+            <v>0.28103151374638402</v>
           </cell>
           <cell r="G6">
-            <v>0.18398203276660599</v>
+            <v>0.21456750872458</v>
           </cell>
           <cell r="H6">
-            <v>1</v>
+            <v>1.1200000000000001</v>
           </cell>
           <cell r="I6">
-            <v>3.2646386575724898E-2</v>
+            <v>3.5110423411378301E-2</v>
           </cell>
           <cell r="J6">
-            <v>2.8700340830130601E-2</v>
+            <v>3.1880713374243502E-2</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7" t="str">
+            <v>fut_ESM1-2-LR_SSP370_constVolc</v>
+          </cell>
+          <cell r="C7">
+            <v>0.54619910490746704</v>
+          </cell>
+          <cell r="D7">
+            <v>0.85026964875689004</v>
+          </cell>
+          <cell r="E7">
+            <v>0.99999836434091705</v>
+          </cell>
+          <cell r="F7">
+            <v>0.35236140573901098</v>
+          </cell>
+          <cell r="G7">
+            <v>0.27106817338542499</v>
+          </cell>
+          <cell r="H7">
+            <v>1.08</v>
+          </cell>
+          <cell r="I7">
+            <v>3.67655115767027E-2</v>
+          </cell>
+          <cell r="J7">
+            <v>3.35054597998811E-2</v>
           </cell>
         </row>
         <row r="8">
@@ -792,28 +913,57 @@
             <v>fut_NorESM_RCP45_Volc</v>
           </cell>
           <cell r="C8">
-            <v>0.31504677447179003</v>
+            <v>0.307948440316553</v>
           </cell>
           <cell r="D8">
-            <v>0.57232123229446896</v>
+            <v>0.56086887661448304</v>
           </cell>
           <cell r="E8">
-            <v>0.89159107765915202</v>
+            <v>0.88328191599981898</v>
           </cell>
           <cell r="F8">
-            <v>0.65038981916972405</v>
+            <v>0.68845574872436999</v>
           </cell>
           <cell r="G8">
-            <v>0.69969231489820405</v>
+            <v>0.73625220438107497</v>
           </cell>
           <cell r="H8">
+            <v>1.11666666666666</v>
+          </cell>
+          <cell r="I8">
+            <v>5.2707464159806802E-2</v>
+          </cell>
+          <cell r="J8">
+            <v>5.4510865770008098E-2</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9" t="str">
+            <v>fut_NorESM_RCP45_Volc</v>
+          </cell>
+          <cell r="C9">
+            <v>0.295802697172452</v>
+          </cell>
+          <cell r="D9">
+            <v>0.54277920035025196</v>
+          </cell>
+          <cell r="E9">
+            <v>0.87879965089157297</v>
+          </cell>
+          <cell r="F9">
+            <v>0.71051840812753497</v>
+          </cell>
+          <cell r="G9">
+            <v>0.77054138023377905</v>
+          </cell>
+          <cell r="H9">
             <v>1.1000000000000001</v>
           </cell>
-          <cell r="I8">
-            <v>4.9608096699926101E-2</v>
-          </cell>
-          <cell r="J8">
-            <v>5.1449692451564499E-2</v>
+          <cell r="I9">
+            <v>4.9516240832959101E-2</v>
+          </cell>
+          <cell r="J9">
+            <v>5.1047676785816301E-2</v>
           </cell>
         </row>
         <row r="10">
@@ -821,28 +971,57 @@
             <v>fut_NorESM_RCP45_VolcConst</v>
           </cell>
           <cell r="C10">
-            <v>0.60445409265483296</v>
+            <v>0.54514943518981696</v>
           </cell>
           <cell r="D10">
-            <v>0.91644379909259599</v>
+            <v>0.87461617266192504</v>
           </cell>
           <cell r="E10">
-            <v>0.99999999918240301</v>
+            <v>0.99999951520399999</v>
           </cell>
           <cell r="F10">
-            <v>0.39538783081048301</v>
+            <v>0.43700824798559201</v>
           </cell>
           <cell r="G10">
-            <v>0.42024078216599597</v>
+            <v>0.46820692982842599</v>
           </cell>
           <cell r="H10">
+            <v>1</v>
+          </cell>
+          <cell r="I10">
+            <v>3.0552993250828501E-2</v>
+          </cell>
+          <cell r="J10">
+            <v>3.1015313492675101E-2</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11" t="str">
+            <v>fut_NorESM_RCP45_VolcConst</v>
+          </cell>
+          <cell r="C11">
+            <v>0.53338404346295398</v>
+          </cell>
+          <cell r="D11">
+            <v>0.87097082324211506</v>
+          </cell>
+          <cell r="E11">
+            <v>0.99999430169446302</v>
+          </cell>
+          <cell r="F11">
+            <v>0.59136052630917102</v>
+          </cell>
+          <cell r="G11">
+            <v>0.62348162834786303</v>
+          </cell>
+          <cell r="H11">
             <v>1.0166666666666599</v>
           </cell>
-          <cell r="I10">
-            <v>2.8010350719259801E-2</v>
-          </cell>
-          <cell r="J10">
-            <v>2.7966801098772701E-2</v>
+          <cell r="I11">
+            <v>3.00118195904426E-2</v>
+          </cell>
+          <cell r="J11">
+            <v>3.0029336713997799E-2</v>
           </cell>
         </row>
       </sheetData>
@@ -858,37 +1037,95 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="final_combined_7methods_wide_ff"/>
+      <sheetName val="final_combined_16methods_wide_f"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
+        <row r="2">
+          <cell r="A2" t="str">
+            <v>fut_ESM1-2-LR_SSP126_constVolc</v>
+          </cell>
+          <cell r="C2">
+            <v>0.21863766120108799</v>
+          </cell>
+          <cell r="D2">
+            <v>0.41443677964713499</v>
+          </cell>
+          <cell r="E2">
+            <v>0.77937568423139103</v>
+          </cell>
+          <cell r="F2">
+            <v>0.48696744999126601</v>
+          </cell>
+          <cell r="G2">
+            <v>0.51389146851774203</v>
+          </cell>
+          <cell r="H2">
+            <v>1.32</v>
+          </cell>
+          <cell r="I2">
+            <v>3.50856668376376E-2</v>
+          </cell>
+          <cell r="J2">
+            <v>3.3615419242651802E-2</v>
+          </cell>
+        </row>
         <row r="3">
           <cell r="A3" t="str">
             <v>fut_ESM1-2-LR_SSP126_constVolc</v>
           </cell>
           <cell r="C3">
-            <v>0.20598707423877799</v>
+            <v>0.20576812891627</v>
           </cell>
           <cell r="D3">
-            <v>0.39125892210348001</v>
+            <v>0.39131798477193203</v>
           </cell>
           <cell r="E3">
-            <v>0.75460221525915105</v>
+            <v>0.75985380247993595</v>
           </cell>
           <cell r="F3">
-            <v>0.56475621844510304</v>
+            <v>0.555132277466724</v>
           </cell>
           <cell r="G3">
-            <v>0</v>
+            <v>0.58900071435593904</v>
           </cell>
           <cell r="H3">
-            <v>1.42</v>
+            <v>1.32</v>
           </cell>
           <cell r="I3">
-            <v>3.52982195739854E-2</v>
+            <v>3.5373468407243903E-2</v>
           </cell>
           <cell r="J3">
-            <v>3.4435063627015101E-2</v>
+            <v>3.4498382156762097E-2</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4" t="str">
+            <v>fut_ESM1-2-LR_SSP245_constVolc</v>
+          </cell>
+          <cell r="C4">
+            <v>0.50241628034270402</v>
+          </cell>
+          <cell r="D4">
+            <v>0.80083031539555205</v>
+          </cell>
+          <cell r="E4">
+            <v>0.98233423425677902</v>
+          </cell>
+          <cell r="F4">
+            <v>0.37766050566306703</v>
+          </cell>
+          <cell r="G4">
+            <v>0.36062433239381603</v>
+          </cell>
+          <cell r="H4">
+            <v>1.04</v>
+          </cell>
+          <cell r="I4">
+            <v>3.3762834915676602E-2</v>
+          </cell>
+          <cell r="J4">
+            <v>3.1137489609733799E-2</v>
           </cell>
         </row>
         <row r="5">
@@ -896,28 +1133,57 @@
             <v>fut_ESM1-2-LR_SSP245_constVolc</v>
           </cell>
           <cell r="C5">
-            <v>0.54537720214768104</v>
+            <v>0.55327213342940795</v>
           </cell>
           <cell r="D5">
-            <v>0.82936652432745805</v>
+            <v>0.83542228277474595</v>
           </cell>
           <cell r="E5">
-            <v>0.98938446493499099</v>
+            <v>0.99065301016602703</v>
           </cell>
           <cell r="F5">
-            <v>0.47702824636535701</v>
+            <v>0.474326788739316</v>
           </cell>
           <cell r="G5">
-            <v>0</v>
+            <v>0.46525764271050302</v>
           </cell>
           <cell r="H5">
+            <v>1.08</v>
+          </cell>
+          <cell r="I5">
+            <v>3.2244062898479302E-2</v>
+          </cell>
+          <cell r="J5">
+            <v>3.00446004526808E-2</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6" t="str">
+            <v>fut_ESM1-2-LR_SSP370_constVolc</v>
+          </cell>
+          <cell r="C6">
+            <v>0.53501465488853195</v>
+          </cell>
+          <cell r="D6">
+            <v>0.84813894955111901</v>
+          </cell>
+          <cell r="E6">
+            <v>0.99999924843690502</v>
+          </cell>
+          <cell r="F6">
+            <v>0.30089129959560101</v>
+          </cell>
+          <cell r="G6">
+            <v>0.205675254798835</v>
+          </cell>
+          <cell r="H6">
             <v>1.04</v>
           </cell>
-          <cell r="I5">
-            <v>3.20702585058706E-2</v>
-          </cell>
-          <cell r="J5">
-            <v>2.9932675985723699E-2</v>
+          <cell r="I6">
+            <v>3.6451904631969602E-2</v>
+          </cell>
+          <cell r="J6">
+            <v>3.0872821507860401E-2</v>
           </cell>
         </row>
         <row r="7">
@@ -925,28 +1191,57 @@
             <v>fut_ESM1-2-LR_SSP370_constVolc</v>
           </cell>
           <cell r="C7">
-            <v>0.54377625772486804</v>
+            <v>0.55738744535778695</v>
           </cell>
           <cell r="D7">
-            <v>0.85010427686262902</v>
+            <v>0.85120073146078801</v>
           </cell>
           <cell r="E7">
-            <v>0.99999241359801805</v>
+            <v>0.99999778206774803</v>
           </cell>
           <cell r="F7">
-            <v>0.35240261158414299</v>
+            <v>0.34517946300421798</v>
           </cell>
           <cell r="G7">
-            <v>0</v>
+            <v>0.26883137024650899</v>
           </cell>
           <cell r="H7">
-            <v>1.08</v>
+            <v>1.06</v>
           </cell>
           <cell r="I7">
-            <v>3.6908175403974099E-2</v>
+            <v>3.6506341264737098E-2</v>
           </cell>
           <cell r="J7">
-            <v>3.3497276994360899E-2</v>
+            <v>3.3248760486993302E-2</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8" t="str">
+            <v>fut_NorESM_RCP45_Volc</v>
+          </cell>
+          <cell r="C8">
+            <v>0.31140257165176499</v>
+          </cell>
+          <cell r="D8">
+            <v>0.56608191326903601</v>
+          </cell>
+          <cell r="E8">
+            <v>0.88269092438697105</v>
+          </cell>
+          <cell r="F8">
+            <v>0.67277852547364903</v>
+          </cell>
+          <cell r="G8">
+            <v>0.71152466033224304</v>
+          </cell>
+          <cell r="H8">
+            <v>1.1000000000000001</v>
+          </cell>
+          <cell r="I8">
+            <v>5.1493484708925202E-2</v>
+          </cell>
+          <cell r="J8">
+            <v>5.2810633513484799E-2</v>
           </cell>
         </row>
         <row r="9">
@@ -954,28 +1249,57 @@
             <v>fut_NorESM_RCP45_Volc</v>
           </cell>
           <cell r="C9">
-            <v>0.29728047786762701</v>
+            <v>0.30106359931930998</v>
           </cell>
           <cell r="D9">
-            <v>0.54511819223838698</v>
+            <v>0.55168877761303903</v>
           </cell>
           <cell r="E9">
-            <v>0.87959810607169198</v>
+            <v>0.88473982556344</v>
           </cell>
           <cell r="F9">
-            <v>0.75713434312233396</v>
+            <v>0.72122719204056196</v>
           </cell>
           <cell r="G9">
-            <v>0</v>
+            <v>0.71024730946443604</v>
           </cell>
           <cell r="H9">
-            <v>1.11666666666666</v>
+            <v>1.1000000000000001</v>
           </cell>
           <cell r="I9">
-            <v>4.9593159564462398E-2</v>
+            <v>4.91660796604797E-2</v>
           </cell>
           <cell r="J9">
-            <v>5.1204322773566999E-2</v>
+            <v>5.0769616326947098E-2</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10" t="str">
+            <v>fut_NorESM_RCP45_VolcConst</v>
+          </cell>
+          <cell r="C10">
+            <v>0.54750981158324097</v>
+          </cell>
+          <cell r="D10">
+            <v>0.87561068610950599</v>
+          </cell>
+          <cell r="E10">
+            <v>0.99999991396280796</v>
+          </cell>
+          <cell r="F10">
+            <v>0.42401791056917898</v>
+          </cell>
+          <cell r="G10">
+            <v>0.44634031718390499</v>
+          </cell>
+          <cell r="H10">
+            <v>1</v>
+          </cell>
+          <cell r="I10">
+            <v>2.9801671950952201E-2</v>
+          </cell>
+          <cell r="J10">
+            <v>2.94607743232577E-2</v>
           </cell>
         </row>
         <row r="11">
@@ -983,28 +1307,305 @@
             <v>fut_NorESM_RCP45_VolcConst</v>
           </cell>
           <cell r="C11">
-            <v>0.54102601968391995</v>
+            <v>0.53542936181767697</v>
           </cell>
           <cell r="D11">
-            <v>0.86734724522561701</v>
+            <v>0.86675058660220505</v>
           </cell>
           <cell r="E11">
-            <v>0.99999820550391105</v>
+            <v>0.99999826488588195</v>
           </cell>
           <cell r="F11">
-            <v>0.588634202813348</v>
+            <v>0.56829985226404101</v>
           </cell>
           <cell r="G11">
-            <v>0</v>
+            <v>0.47488218559303003</v>
           </cell>
           <cell r="H11">
-            <v>1</v>
+            <v>1.0166666666666599</v>
           </cell>
           <cell r="I11">
-            <v>2.9942905637516601E-2</v>
+            <v>2.9692821763125501E-2</v>
           </cell>
           <cell r="J11">
-            <v>3.0024013511340601E-2</v>
+            <v>2.9527986662152901E-2</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="final_combined_32methods_wide_f"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="C2">
+            <v>0.232929713919617</v>
+          </cell>
+          <cell r="D2">
+            <v>0.437810418972361</v>
+          </cell>
+          <cell r="E2">
+            <v>0.79678814890417904</v>
+          </cell>
+          <cell r="F2">
+            <v>0.49141179481859698</v>
+          </cell>
+          <cell r="G2">
+            <v>0.53467197927883603</v>
+          </cell>
+          <cell r="H2">
+            <v>1.42</v>
+          </cell>
+          <cell r="I2">
+            <v>3.5518948759835502E-2</v>
+          </cell>
+          <cell r="J2">
+            <v>3.53737882916575E-2</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="C3">
+            <v>0.21789558676590701</v>
+          </cell>
+          <cell r="D3">
+            <v>0.41545942039553602</v>
+          </cell>
+          <cell r="E3">
+            <v>0.79430186547134896</v>
+          </cell>
+          <cell r="F3">
+            <v>0.55355925523003502</v>
+          </cell>
+          <cell r="G3">
+            <v>0.58926144099300404</v>
+          </cell>
+          <cell r="H3">
+            <v>1.32</v>
+          </cell>
+          <cell r="I3">
+            <v>3.4759033290035199E-2</v>
+          </cell>
+          <cell r="J3">
+            <v>3.4058045419036002E-2</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="C4">
+            <v>0.53099357414290005</v>
+          </cell>
+          <cell r="D4">
+            <v>0.82487087083286303</v>
+          </cell>
+          <cell r="E4">
+            <v>0.99032480491036301</v>
+          </cell>
+          <cell r="F4">
+            <v>0.35769399037726202</v>
+          </cell>
+          <cell r="G4">
+            <v>0.35330599421387099</v>
+          </cell>
+          <cell r="H4">
+            <v>1.04</v>
+          </cell>
+          <cell r="I4">
+            <v>3.2180212168593798E-2</v>
+          </cell>
+          <cell r="J4">
+            <v>3.06081086701467E-2</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="C5">
+            <v>0.53795071414849205</v>
+          </cell>
+          <cell r="D5">
+            <v>0.82966165685017401</v>
+          </cell>
+          <cell r="E5">
+            <v>0.99279793965561802</v>
+          </cell>
+          <cell r="F5">
+            <v>0.47296562334456499</v>
+          </cell>
+          <cell r="G5">
+            <v>0.46616316879048197</v>
+          </cell>
+          <cell r="H5">
+            <v>1.06</v>
+          </cell>
+          <cell r="I5">
+            <v>3.1879531639024898E-2</v>
+          </cell>
+          <cell r="J5">
+            <v>2.9940485328590699E-2</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="C6">
+            <v>0.57071574749153098</v>
+          </cell>
+          <cell r="D6">
+            <v>0.86860141429073801</v>
+          </cell>
+          <cell r="E6">
+            <v>0.99999963584588902</v>
+          </cell>
+          <cell r="F6">
+            <v>0.29445999120060601</v>
+          </cell>
+          <cell r="G6">
+            <v>0.23833676480029001</v>
+          </cell>
+          <cell r="H6">
+            <v>1.06</v>
+          </cell>
+          <cell r="I6">
+            <v>3.58686394015027E-2</v>
+          </cell>
+          <cell r="J6">
+            <v>3.3520742091611301E-2</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="C7">
+            <v>0.54447939616679597</v>
+          </cell>
+          <cell r="D7">
+            <v>0.84570767317965201</v>
+          </cell>
+          <cell r="E7">
+            <v>0.99999336318933896</v>
+          </cell>
+          <cell r="F7">
+            <v>0.35570970869045898</v>
+          </cell>
+          <cell r="G7">
+            <v>0.27231278148992299</v>
+          </cell>
+          <cell r="H7">
+            <v>1.06</v>
+          </cell>
+          <cell r="I7">
+            <v>3.7020164041822297E-2</v>
+          </cell>
+          <cell r="J7">
+            <v>3.3484937846857799E-2</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="C8">
+            <v>0.30728740459515103</v>
+          </cell>
+          <cell r="D8">
+            <v>0.56063420527432195</v>
+          </cell>
+          <cell r="E8">
+            <v>0.88528731731210597</v>
+          </cell>
+          <cell r="F8">
+            <v>0.67512915843021004</v>
+          </cell>
+          <cell r="G8">
+            <v>0.70899514228895699</v>
+          </cell>
+          <cell r="H8">
+            <v>1.1499999999999999</v>
+          </cell>
+          <cell r="I8">
+            <v>5.1485888988200099E-2</v>
+          </cell>
+          <cell r="J8">
+            <v>5.2533223607533798E-2</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="C9">
+            <v>0.32645120923792798</v>
+          </cell>
+          <cell r="D9">
+            <v>0.59079979067163901</v>
+          </cell>
+          <cell r="E9">
+            <v>0.90896191913690905</v>
+          </cell>
+          <cell r="F9">
+            <v>0.73645404524055702</v>
+          </cell>
+          <cell r="G9">
+            <v>0.81387864681549205</v>
+          </cell>
+          <cell r="H9">
+            <v>1.0833333333333299</v>
+          </cell>
+          <cell r="I9">
+            <v>4.8982929865659303E-2</v>
+          </cell>
+          <cell r="J9">
+            <v>5.0659588379776799E-2</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="C10">
+            <v>0.56090986534166298</v>
+          </cell>
+          <cell r="D10">
+            <v>0.88161955063888198</v>
+          </cell>
+          <cell r="E10">
+            <v>0.99999974469155095</v>
+          </cell>
+          <cell r="F10">
+            <v>0.41856779286222301</v>
+          </cell>
+          <cell r="G10">
+            <v>0.43694253348560003</v>
+          </cell>
+          <cell r="H10">
+            <v>1.0166666666666599</v>
+          </cell>
+          <cell r="I10">
+            <v>2.9465985614831301E-2</v>
+          </cell>
+          <cell r="J10">
+            <v>2.8759257707692599E-2</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="C11">
+            <v>0.54497070338604503</v>
+          </cell>
+          <cell r="D11">
+            <v>0.869225259621072</v>
+          </cell>
+          <cell r="E11">
+            <v>0.99999968353572399</v>
+          </cell>
+          <cell r="F11">
+            <v>0.57234286872200302</v>
+          </cell>
+          <cell r="G11">
+            <v>0.59778528724644397</v>
+          </cell>
+          <cell r="H11">
+            <v>1.0166666666666599</v>
+          </cell>
+          <cell r="I11">
+            <v>2.9416336109457701E-2</v>
+          </cell>
+          <cell r="J11">
+            <v>2.9317239210130901E-2</v>
           </cell>
         </row>
       </sheetData>
@@ -1739,7 +2340,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="str">
-        <f>[2]final_combined_7methods_wide_ff!A$7</f>
+        <f>[1]final_combined_7methods_wide_ff!A$7</f>
         <v>fut_ESM1-2-LR_SSP370_constVolc</v>
       </c>
       <c r="B16" t="str">
@@ -1747,41 +2348,41 @@
         <v>ESM1-2-LR_SSP370_constVolc</v>
       </c>
       <c r="C16" s="3">
-        <f>[2]final_combined_7methods_wide_ff!C$7</f>
-        <v>0.54377625772486804</v>
+        <f>[1]final_combined_7methods_wide_ff!C$7</f>
+        <v>0.54619910490746704</v>
       </c>
       <c r="D16" s="3">
-        <f>[2]final_combined_7methods_wide_ff!D$7</f>
-        <v>0.85010427686262902</v>
+        <f>[1]final_combined_7methods_wide_ff!D$7</f>
+        <v>0.85026964875689004</v>
       </c>
       <c r="E16" s="3">
-        <f>[2]final_combined_7methods_wide_ff!E$7</f>
-        <v>0.99999241359801805</v>
+        <f>[1]final_combined_7methods_wide_ff!E$7</f>
+        <v>0.99999836434091705</v>
       </c>
       <c r="F16" s="6">
-        <f>[2]final_combined_7methods_wide_ff!F$7</f>
-        <v>0.35240261158414299</v>
+        <f>[1]final_combined_7methods_wide_ff!F$7</f>
+        <v>0.35236140573901098</v>
       </c>
       <c r="G16" s="6">
-        <f>[2]final_combined_7methods_wide_ff!G$7</f>
-        <v>0</v>
+        <f>[1]final_combined_7methods_wide_ff!G$7</f>
+        <v>0.27106817338542499</v>
       </c>
       <c r="H16" s="6">
-        <f>[2]final_combined_7methods_wide_ff!H$7</f>
+        <f>[1]final_combined_7methods_wide_ff!H$7</f>
         <v>1.08</v>
       </c>
       <c r="I16" s="5">
-        <f>[2]final_combined_7methods_wide_ff!I$7</f>
-        <v>3.6908175403974099E-2</v>
+        <f>[1]final_combined_7methods_wide_ff!I$7</f>
+        <v>3.67655115767027E-2</v>
       </c>
       <c r="J16" s="5">
-        <f>[2]final_combined_7methods_wide_ff!J$7</f>
-        <v>3.3497276994360899E-2</v>
+        <f>[1]final_combined_7methods_wide_ff!J$7</f>
+        <v>3.35054597998811E-2</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" t="str">
-        <f>[2]final_combined_7methods_wide_ff!A$5</f>
+        <f>[1]final_combined_7methods_wide_ff!A$5</f>
         <v>fut_ESM1-2-LR_SSP245_constVolc</v>
       </c>
       <c r="B17" t="str">
@@ -1789,41 +2390,41 @@
         <v>ESM1-2-LR_SSP245_constVolc</v>
       </c>
       <c r="C17" s="3">
-        <f>[2]final_combined_7methods_wide_ff!C$5</f>
-        <v>0.54537720214768104</v>
+        <f>[1]final_combined_7methods_wide_ff!C$5</f>
+        <v>0.55693243562445705</v>
       </c>
       <c r="D17" s="3">
-        <f>[2]final_combined_7methods_wide_ff!D$5</f>
-        <v>0.82936652432745805</v>
+        <f>[1]final_combined_7methods_wide_ff!D$5</f>
+        <v>0.85137216343120803</v>
       </c>
       <c r="E17" s="3">
-        <f>[2]final_combined_7methods_wide_ff!E$5</f>
-        <v>0.98938446493499099</v>
+        <f>[1]final_combined_7methods_wide_ff!E$5</f>
+        <v>0.99159617730083804</v>
       </c>
       <c r="F17" s="6">
-        <f>[2]final_combined_7methods_wide_ff!F$5</f>
-        <v>0.47702824636535701</v>
+        <f>[1]final_combined_7methods_wide_ff!F$5</f>
+        <v>0.48770586775952401</v>
       </c>
       <c r="G17" s="6">
-        <f>[2]final_combined_7methods_wide_ff!G$5</f>
-        <v>0</v>
+        <f>[1]final_combined_7methods_wide_ff!G$5</f>
+        <v>0.48135376341167602</v>
       </c>
       <c r="H17" s="6">
-        <f>[2]final_combined_7methods_wide_ff!H$5</f>
+        <f>[1]final_combined_7methods_wide_ff!H$5</f>
         <v>1.04</v>
       </c>
       <c r="I17" s="5">
-        <f>[2]final_combined_7methods_wide_ff!I$5</f>
-        <v>3.20702585058706E-2</v>
+        <f>[1]final_combined_7methods_wide_ff!I$5</f>
+        <v>3.2207269952229799E-2</v>
       </c>
       <c r="J17" s="5">
-        <f>[2]final_combined_7methods_wide_ff!J$5</f>
-        <v>2.9932675985723699E-2</v>
+        <f>[1]final_combined_7methods_wide_ff!J$5</f>
+        <v>3.0085110989888701E-2</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="str">
-        <f>[2]final_combined_7methods_wide_ff!A$3</f>
+        <f>[1]final_combined_7methods_wide_ff!A$3</f>
         <v>fut_ESM1-2-LR_SSP126_constVolc</v>
       </c>
       <c r="B18" t="str">
@@ -1831,41 +2432,41 @@
         <v>ESM1-2-LR_SSP126_constVolc</v>
       </c>
       <c r="C18" s="3">
-        <f>[2]final_combined_7methods_wide_ff!C$3</f>
-        <v>0.20598707423877799</v>
+        <f>[1]final_combined_7methods_wide_ff!C$3</f>
+        <v>0.20755706849306199</v>
       </c>
       <c r="D18" s="3">
-        <f>[2]final_combined_7methods_wide_ff!D$3</f>
-        <v>0.39125892210348001</v>
+        <f>[1]final_combined_7methods_wide_ff!D$3</f>
+        <v>0.39313285295950501</v>
       </c>
       <c r="E18" s="3">
-        <f>[2]final_combined_7methods_wide_ff!E$3</f>
-        <v>0.75460221525915105</v>
+        <f>[1]final_combined_7methods_wide_ff!E$3</f>
+        <v>0.75508045533102697</v>
       </c>
       <c r="F18" s="6">
-        <f>[2]final_combined_7methods_wide_ff!F$3</f>
-        <v>0.56475621844510304</v>
+        <f>[1]final_combined_7methods_wide_ff!F$3</f>
+        <v>0.56758655826126803</v>
       </c>
       <c r="G18" s="6">
-        <f>[2]final_combined_7methods_wide_ff!G$3</f>
-        <v>0</v>
+        <f>[1]final_combined_7methods_wide_ff!G$3</f>
+        <v>0.60241889512051305</v>
       </c>
       <c r="H18" s="6">
-        <f>[2]final_combined_7methods_wide_ff!H$3</f>
-        <v>1.42</v>
+        <f>[1]final_combined_7methods_wide_ff!H$3</f>
+        <v>1.46</v>
       </c>
       <c r="I18" s="5">
-        <f>[2]final_combined_7methods_wide_ff!I$3</f>
-        <v>3.52982195739854E-2</v>
+        <f>[1]final_combined_7methods_wide_ff!I$3</f>
+        <v>3.55967136847853E-2</v>
       </c>
       <c r="J18" s="5">
-        <f>[2]final_combined_7methods_wide_ff!J$3</f>
-        <v>3.4435063627015101E-2</v>
+        <f>[1]final_combined_7methods_wide_ff!J$3</f>
+        <v>3.4755163366221101E-2</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" t="str">
-        <f>[2]final_combined_7methods_wide_ff!A$11</f>
+        <f>[1]final_combined_7methods_wide_ff!A$11</f>
         <v>fut_NorESM_RCP45_VolcConst</v>
       </c>
       <c r="B19" t="str">
@@ -1873,41 +2474,41 @@
         <v>NorESM_RCP45_VolcConst</v>
       </c>
       <c r="C19" s="3">
-        <f>[2]final_combined_7methods_wide_ff!C$11</f>
-        <v>0.54102601968391995</v>
+        <f>[1]final_combined_7methods_wide_ff!C$11</f>
+        <v>0.53338404346295398</v>
       </c>
       <c r="D19" s="3">
-        <f>[2]final_combined_7methods_wide_ff!D$11</f>
-        <v>0.86734724522561701</v>
+        <f>[1]final_combined_7methods_wide_ff!D$11</f>
+        <v>0.87097082324211506</v>
       </c>
       <c r="E19" s="3">
-        <f>[2]final_combined_7methods_wide_ff!E$11</f>
-        <v>0.99999820550391105</v>
+        <f>[1]final_combined_7methods_wide_ff!E$11</f>
+        <v>0.99999430169446302</v>
       </c>
       <c r="F19" s="6">
-        <f>[2]final_combined_7methods_wide_ff!F$11</f>
-        <v>0.588634202813348</v>
+        <f>[1]final_combined_7methods_wide_ff!F$11</f>
+        <v>0.59136052630917102</v>
       </c>
       <c r="G19" s="6">
-        <f>[2]final_combined_7methods_wide_ff!G$11</f>
-        <v>0</v>
+        <f>[1]final_combined_7methods_wide_ff!G$11</f>
+        <v>0.62348162834786303</v>
       </c>
       <c r="H19" s="6">
-        <f>[2]final_combined_7methods_wide_ff!H$11</f>
-        <v>1</v>
+        <f>[1]final_combined_7methods_wide_ff!H$11</f>
+        <v>1.0166666666666599</v>
       </c>
       <c r="I19" s="5">
-        <f>[2]final_combined_7methods_wide_ff!I$11</f>
-        <v>2.9942905637516601E-2</v>
+        <f>[1]final_combined_7methods_wide_ff!I$11</f>
+        <v>3.00118195904426E-2</v>
       </c>
       <c r="J19" s="5">
-        <f>[2]final_combined_7methods_wide_ff!J$11</f>
-        <v>3.0024013511340601E-2</v>
+        <f>[1]final_combined_7methods_wide_ff!J$11</f>
+        <v>3.0029336713997799E-2</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" t="str">
-        <f>[2]final_combined_7methods_wide_ff!A$9</f>
+        <f>[1]final_combined_7methods_wide_ff!A$9</f>
         <v>fut_NorESM_RCP45_Volc</v>
       </c>
       <c r="B20" t="str">
@@ -1915,36 +2516,36 @@
         <v>NorESM_RCP45_Volc</v>
       </c>
       <c r="C20" s="3">
-        <f>[2]final_combined_7methods_wide_ff!C$9</f>
-        <v>0.29728047786762701</v>
+        <f>[1]final_combined_7methods_wide_ff!C$9</f>
+        <v>0.295802697172452</v>
       </c>
       <c r="D20" s="3">
-        <f>[2]final_combined_7methods_wide_ff!D$9</f>
-        <v>0.54511819223838698</v>
+        <f>[1]final_combined_7methods_wide_ff!D$9</f>
+        <v>0.54277920035025196</v>
       </c>
       <c r="E20" s="3">
-        <f>[2]final_combined_7methods_wide_ff!E$9</f>
-        <v>0.87959810607169198</v>
+        <f>[1]final_combined_7methods_wide_ff!E$9</f>
+        <v>0.87879965089157297</v>
       </c>
       <c r="F20" s="6">
-        <f>[2]final_combined_7methods_wide_ff!F$9</f>
-        <v>0.75713434312233396</v>
+        <f>[1]final_combined_7methods_wide_ff!F$9</f>
+        <v>0.71051840812753497</v>
       </c>
       <c r="G20" s="6">
-        <f>[2]final_combined_7methods_wide_ff!G$9</f>
-        <v>0</v>
+        <f>[1]final_combined_7methods_wide_ff!G$9</f>
+        <v>0.77054138023377905</v>
       </c>
       <c r="H20" s="6">
-        <f>[2]final_combined_7methods_wide_ff!H$9</f>
-        <v>1.11666666666666</v>
+        <f>[1]final_combined_7methods_wide_ff!H$9</f>
+        <v>1.1000000000000001</v>
       </c>
       <c r="I20" s="5">
-        <f>[2]final_combined_7methods_wide_ff!I$9</f>
-        <v>4.9593159564462398E-2</v>
+        <f>[1]final_combined_7methods_wide_ff!I$9</f>
+        <v>4.9516240832959101E-2</v>
       </c>
       <c r="J20" s="5">
-        <f>[2]final_combined_7methods_wide_ff!J$9</f>
-        <v>5.1204322773566999E-2</v>
+        <f>[1]final_combined_7methods_wide_ff!J$9</f>
+        <v>5.1047676785816301E-2</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
@@ -1961,7 +2562,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" t="str">
-        <f>[1]final_combined_16methods_wide_f!A$2</f>
+        <f>[2]final_combined_16methods_wide_f!A$2</f>
         <v>fut_ESM1-2-LR_SSP126_constVolc</v>
       </c>
       <c r="B23" t="str">
@@ -1969,41 +2570,41 @@
         <v>ESM1-2-LR_SSP126_constVolc</v>
       </c>
       <c r="C23" s="3">
-        <f>[1]final_combined_16methods_wide_f!C$2</f>
-        <v>0.23423231205582501</v>
+        <f>[2]final_combined_16methods_wide_f!C$2</f>
+        <v>0.21863766120108799</v>
       </c>
       <c r="D23" s="3">
-        <f>[1]final_combined_16methods_wide_f!D$2</f>
-        <v>0.44301513220746003</v>
+        <f>[2]final_combined_16methods_wide_f!D$2</f>
+        <v>0.41443677964713499</v>
       </c>
       <c r="E23" s="3">
-        <f>[1]final_combined_16methods_wide_f!E$2</f>
-        <v>0.80477747916472697</v>
+        <f>[2]final_combined_16methods_wide_f!E$2</f>
+        <v>0.77937568423139103</v>
       </c>
       <c r="F23" s="2">
-        <f>[1]final_combined_16methods_wide_f!F$2</f>
-        <v>0.46624181380279101</v>
+        <f>[2]final_combined_16methods_wide_f!F$2</f>
+        <v>0.48696744999126601</v>
       </c>
       <c r="G23" s="2">
-        <f>[1]final_combined_16methods_wide_f!G$2</f>
-        <v>0.49304442107483998</v>
+        <f>[2]final_combined_16methods_wide_f!G$2</f>
+        <v>0.51389146851774203</v>
       </c>
       <c r="H23" s="2">
-        <f>[1]final_combined_16methods_wide_f!H$2</f>
-        <v>1.22</v>
+        <f>[2]final_combined_16methods_wide_f!H$2</f>
+        <v>1.32</v>
       </c>
       <c r="I23" s="1">
-        <f>[1]final_combined_16methods_wide_f!I$2</f>
-        <v>3.4209966316283001E-2</v>
+        <f>[2]final_combined_16methods_wide_f!I$2</f>
+        <v>3.50856668376376E-2</v>
       </c>
       <c r="J23" s="1">
-        <f>[1]final_combined_16methods_wide_f!J$2</f>
-        <v>3.3170670153985497E-2</v>
+        <f>[2]final_combined_16methods_wide_f!J$2</f>
+        <v>3.3615419242651802E-2</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" t="str">
-        <f>[1]final_combined_16methods_wide_f!A$4</f>
+        <f>[2]final_combined_16methods_wide_f!A$4</f>
         <v>fut_ESM1-2-LR_SSP245_constVolc</v>
       </c>
       <c r="B24" t="str">
@@ -2011,41 +2612,41 @@
         <v>ESM1-2-LR_SSP245_constVolc</v>
       </c>
       <c r="C24" s="3">
-        <f>[1]final_combined_16methods_wide_f!C$4</f>
-        <v>0.54526216461403398</v>
+        <f>[2]final_combined_16methods_wide_f!C$4</f>
+        <v>0.50241628034270402</v>
       </c>
       <c r="D24" s="3">
-        <f>[1]final_combined_16methods_wide_f!D$4</f>
-        <v>0.85151612528392695</v>
+        <f>[2]final_combined_16methods_wide_f!D$4</f>
+        <v>0.80083031539555205</v>
       </c>
       <c r="E24" s="3">
-        <f>[1]final_combined_16methods_wide_f!E$4</f>
-        <v>0.98769878415374102</v>
+        <f>[2]final_combined_16methods_wide_f!E$4</f>
+        <v>0.98233423425677902</v>
       </c>
       <c r="F24" s="2">
-        <f>[1]final_combined_16methods_wide_f!F$4</f>
-        <v>0.34391488294497302</v>
+        <f>[2]final_combined_16methods_wide_f!F$4</f>
+        <v>0.37766050566306703</v>
       </c>
       <c r="G24" s="2">
-        <f>[1]final_combined_16methods_wide_f!G$4</f>
-        <v>0.33005863001684399</v>
+        <f>[2]final_combined_16methods_wide_f!G$4</f>
+        <v>0.36062433239381603</v>
       </c>
       <c r="H24" s="2">
-        <f>[1]final_combined_16methods_wide_f!H$4</f>
-        <v>1.02</v>
+        <f>[2]final_combined_16methods_wide_f!H$4</f>
+        <v>1.04</v>
       </c>
       <c r="I24" s="1">
-        <f>[1]final_combined_16methods_wide_f!I$4</f>
-        <v>3.1604406760897701E-2</v>
+        <f>[2]final_combined_16methods_wide_f!I$4</f>
+        <v>3.3762834915676602E-2</v>
       </c>
       <c r="J24" s="1">
-        <f>[1]final_combined_16methods_wide_f!J$4</f>
-        <v>2.94731342330086E-2</v>
+        <f>[2]final_combined_16methods_wide_f!J$4</f>
+        <v>3.1137489609733799E-2</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" t="str">
-        <f>[1]final_combined_16methods_wide_f!A$6</f>
+        <f>[2]final_combined_16methods_wide_f!A$6</f>
         <v>fut_ESM1-2-LR_SSP370_constVolc</v>
       </c>
       <c r="B25" t="str">
@@ -2053,41 +2654,41 @@
         <v>ESM1-2-LR_SSP370_constVolc</v>
       </c>
       <c r="C25" s="3">
-        <f>[1]final_combined_16methods_wide_f!C$6</f>
-        <v>0.58820103523420497</v>
+        <f>[2]final_combined_16methods_wide_f!C$6</f>
+        <v>0.53501465488853195</v>
       </c>
       <c r="D25" s="3">
-        <f>[1]final_combined_16methods_wide_f!D$6</f>
-        <v>0.882503084666731</v>
+        <f>[2]final_combined_16methods_wide_f!D$6</f>
+        <v>0.84813894955111901</v>
       </c>
       <c r="E25" s="3">
-        <f>[1]final_combined_16methods_wide_f!E$6</f>
-        <v>0.99999998110849297</v>
+        <f>[2]final_combined_16methods_wide_f!E$6</f>
+        <v>0.99999924843690502</v>
       </c>
       <c r="F25" s="2">
-        <f>[1]final_combined_16methods_wide_f!F$6</f>
-        <v>0.25605969664375</v>
+        <f>[2]final_combined_16methods_wide_f!F$6</f>
+        <v>0.30089129959560101</v>
       </c>
       <c r="G25" s="2">
-        <f>[1]final_combined_16methods_wide_f!G$6</f>
-        <v>0.18398203276660599</v>
+        <f>[2]final_combined_16methods_wide_f!G$6</f>
+        <v>0.205675254798835</v>
       </c>
       <c r="H25" s="2">
-        <f>[1]final_combined_16methods_wide_f!H$6</f>
-        <v>1</v>
+        <f>[2]final_combined_16methods_wide_f!H$6</f>
+        <v>1.04</v>
       </c>
       <c r="I25" s="1">
-        <f>[1]final_combined_16methods_wide_f!I$6</f>
-        <v>3.2646386575724898E-2</v>
+        <f>[2]final_combined_16methods_wide_f!I$6</f>
+        <v>3.6451904631969602E-2</v>
       </c>
       <c r="J25" s="1">
-        <f>[1]final_combined_16methods_wide_f!J$6</f>
-        <v>2.8700340830130601E-2</v>
+        <f>[2]final_combined_16methods_wide_f!J$6</f>
+        <v>3.0872821507860401E-2</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" t="str">
-        <f>[1]final_combined_16methods_wide_f!A$8</f>
+        <f>[2]final_combined_16methods_wide_f!A$8</f>
         <v>fut_NorESM_RCP45_Volc</v>
       </c>
       <c r="B26" t="str">
@@ -2095,41 +2696,41 @@
         <v>NorESM_RCP45_Volc</v>
       </c>
       <c r="C26" s="3">
-        <f>[1]final_combined_16methods_wide_f!C$8</f>
-        <v>0.31504677447179003</v>
+        <f>[2]final_combined_16methods_wide_f!C$8</f>
+        <v>0.31140257165176499</v>
       </c>
       <c r="D26" s="3">
-        <f>[1]final_combined_16methods_wide_f!D$8</f>
-        <v>0.57232123229446896</v>
+        <f>[2]final_combined_16methods_wide_f!D$8</f>
+        <v>0.56608191326903601</v>
       </c>
       <c r="E26" s="3">
-        <f>[1]final_combined_16methods_wide_f!E$8</f>
-        <v>0.89159107765915202</v>
+        <f>[2]final_combined_16methods_wide_f!E$8</f>
+        <v>0.88269092438697105</v>
       </c>
       <c r="F26" s="2">
-        <f>[1]final_combined_16methods_wide_f!F$8</f>
-        <v>0.65038981916972405</v>
+        <f>[2]final_combined_16methods_wide_f!F$8</f>
+        <v>0.67277852547364903</v>
       </c>
       <c r="G26" s="2">
-        <f>[1]final_combined_16methods_wide_f!G$8</f>
-        <v>0.69969231489820405</v>
+        <f>[2]final_combined_16methods_wide_f!G$8</f>
+        <v>0.71152466033224304</v>
       </c>
       <c r="H26" s="2">
-        <f>[1]final_combined_16methods_wide_f!H$8</f>
+        <f>[2]final_combined_16methods_wide_f!H$8</f>
         <v>1.1000000000000001</v>
       </c>
       <c r="I26" s="1">
-        <f>[1]final_combined_16methods_wide_f!I$8</f>
-        <v>4.9608096699926101E-2</v>
+        <f>[2]final_combined_16methods_wide_f!I$8</f>
+        <v>5.1493484708925202E-2</v>
       </c>
       <c r="J26" s="1">
-        <f>[1]final_combined_16methods_wide_f!J$8</f>
-        <v>5.1449692451564499E-2</v>
+        <f>[2]final_combined_16methods_wide_f!J$8</f>
+        <v>5.2810633513484799E-2</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" t="str">
-        <f>[1]final_combined_16methods_wide_f!A$10</f>
+        <f>[2]final_combined_16methods_wide_f!A$10</f>
         <v>fut_NorESM_RCP45_VolcConst</v>
       </c>
       <c r="B27" t="str">
@@ -2137,36 +2738,36 @@
         <v>NorESM_RCP45_VolcConst</v>
       </c>
       <c r="C27" s="3">
-        <f>[1]final_combined_16methods_wide_f!C$10</f>
-        <v>0.60445409265483296</v>
+        <f>[2]final_combined_16methods_wide_f!C$10</f>
+        <v>0.54750981158324097</v>
       </c>
       <c r="D27" s="3">
-        <f>[1]final_combined_16methods_wide_f!D$10</f>
-        <v>0.91644379909259599</v>
+        <f>[2]final_combined_16methods_wide_f!D$10</f>
+        <v>0.87561068610950599</v>
       </c>
       <c r="E27" s="3">
-        <f>[1]final_combined_16methods_wide_f!E$10</f>
-        <v>0.99999999918240301</v>
+        <f>[2]final_combined_16methods_wide_f!E$10</f>
+        <v>0.99999991396280796</v>
       </c>
       <c r="F27" s="2">
-        <f>[1]final_combined_16methods_wide_f!F$10</f>
-        <v>0.39538783081048301</v>
+        <f>[2]final_combined_16methods_wide_f!F$10</f>
+        <v>0.42401791056917898</v>
       </c>
       <c r="G27" s="2">
-        <f>[1]final_combined_16methods_wide_f!G$10</f>
-        <v>0.42024078216599597</v>
+        <f>[2]final_combined_16methods_wide_f!G$10</f>
+        <v>0.44634031718390499</v>
       </c>
       <c r="H27" s="2">
-        <f>[1]final_combined_16methods_wide_f!H$10</f>
-        <v>1.0166666666666599</v>
+        <f>[2]final_combined_16methods_wide_f!H$10</f>
+        <v>1</v>
       </c>
       <c r="I27" s="1">
-        <f>[1]final_combined_16methods_wide_f!I$10</f>
-        <v>2.8010350719259801E-2</v>
+        <f>[2]final_combined_16methods_wide_f!I$10</f>
+        <v>2.9801671950952201E-2</v>
       </c>
       <c r="J27" s="1">
-        <f>[1]final_combined_16methods_wide_f!J$10</f>
-        <v>2.7966801098772701E-2</v>
+        <f>[2]final_combined_16methods_wide_f!J$10</f>
+        <v>2.94607743232577E-2</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
@@ -2201,35 +2802,35 @@
         <v>ESM1-2-LR_SSP370_constVolc</v>
       </c>
       <c r="C30" s="3">
-        <f>C6</f>
+        <f t="shared" ref="C30:J30" si="1">C6</f>
         <v>0.64167468205339295</v>
       </c>
       <c r="D30" s="3">
-        <f>D6</f>
+        <f t="shared" si="1"/>
         <v>0.92134192098814205</v>
       </c>
       <c r="E30" s="3">
-        <f>E6</f>
+        <f t="shared" si="1"/>
         <v>0.99999999992211497</v>
       </c>
       <c r="F30" s="2">
-        <f>F6</f>
+        <f t="shared" si="1"/>
         <v>0.58257242065806303</v>
       </c>
       <c r="G30" s="2">
-        <f>G6</f>
+        <f t="shared" si="1"/>
         <v>0.36471938323216702</v>
       </c>
       <c r="H30" s="2">
-        <f>H6</f>
+        <f t="shared" si="1"/>
         <v>1.06</v>
       </c>
       <c r="I30" s="1">
-        <f>I6</f>
+        <f t="shared" si="1"/>
         <v>3.9146185155741801E-2</v>
       </c>
       <c r="J30" s="1">
-        <f>J6</f>
+        <f t="shared" si="1"/>
         <v>2.9479803361305599E-2</v>
       </c>
     </row>
@@ -2243,35 +2844,35 @@
         <v>ESM1-2-LR_SSP245_constVolc</v>
       </c>
       <c r="C31" s="3">
-        <f t="shared" ref="C31:J31" si="1">C4</f>
+        <f t="shared" ref="C31:J31" si="2">C4</f>
         <v>0.50974682042109598</v>
       </c>
       <c r="D31" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.80996193536411498</v>
       </c>
       <c r="E31" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.98746274665149802</v>
       </c>
       <c r="F31" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.56415571141182597</v>
       </c>
       <c r="G31" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.39092663554097901</v>
       </c>
       <c r="H31" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.02</v>
       </c>
       <c r="I31" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.9619484294593298E-2</v>
       </c>
       <c r="J31" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.2487978546580497E-2</v>
       </c>
     </row>
@@ -2285,35 +2886,35 @@
         <v>ESM1-2-LR_SSP126_constVolc</v>
       </c>
       <c r="C32" s="3">
-        <f>C2</f>
+        <f t="shared" ref="C32:J32" si="3">C2</f>
         <v>0.21161932405351599</v>
       </c>
       <c r="D32" s="3">
-        <f>D2</f>
+        <f t="shared" si="3"/>
         <v>0.40396595365675098</v>
       </c>
       <c r="E32" s="3">
-        <f>E2</f>
+        <f t="shared" si="3"/>
         <v>0.76865427585143098</v>
       </c>
       <c r="F32" s="2">
-        <f>F2</f>
+        <f t="shared" si="3"/>
         <v>0.63734650833749396</v>
       </c>
       <c r="G32" s="2">
-        <f>G2</f>
+        <f t="shared" si="3"/>
         <v>0.52549062434882099</v>
       </c>
       <c r="H32" s="2">
-        <f>H2</f>
+        <f t="shared" si="3"/>
         <v>1.54</v>
       </c>
       <c r="I32" s="1">
-        <f>I2</f>
+        <f t="shared" si="3"/>
         <v>4.14550484967314E-2</v>
       </c>
       <c r="J32" s="1">
-        <f>J2</f>
+        <f t="shared" si="3"/>
         <v>3.5818757452349699E-2</v>
       </c>
     </row>
@@ -2327,35 +2928,35 @@
         <v>NorESM_RCP45_VolcConst</v>
       </c>
       <c r="C33" s="3">
-        <f>C10</f>
+        <f t="shared" ref="C33:J33" si="4">C10</f>
         <v>0.49934996162543499</v>
       </c>
       <c r="D33" s="3">
-        <f>D10</f>
+        <f t="shared" si="4"/>
         <v>0.85184374092964499</v>
       </c>
       <c r="E33" s="3">
-        <f>E10</f>
+        <f t="shared" si="4"/>
         <v>0.99999419553518598</v>
       </c>
       <c r="F33" s="2">
-        <f>F10</f>
+        <f t="shared" si="4"/>
         <v>0.57230663609077204</v>
       </c>
       <c r="G33" s="2">
-        <f>G10</f>
+        <f t="shared" si="4"/>
         <v>0.42470431846740098</v>
       </c>
       <c r="H33" s="2">
-        <f>H10</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="I33" s="1">
-        <f>I10</f>
+        <f t="shared" si="4"/>
         <v>2.9102690918756099E-2</v>
       </c>
       <c r="J33" s="1">
-        <f>J10</f>
+        <f t="shared" si="4"/>
         <v>2.49146921749391E-2</v>
       </c>
     </row>
@@ -2369,35 +2970,35 @@
         <v>NorESM_RCP45_Volc</v>
       </c>
       <c r="C34" s="3">
-        <f>C8</f>
+        <f t="shared" ref="C34:J34" si="5">C8</f>
         <v>0.35316813126645102</v>
       </c>
       <c r="D34" s="3">
-        <f>D8</f>
+        <f t="shared" si="5"/>
         <v>0.62991221212830595</v>
       </c>
       <c r="E34" s="3">
-        <f>E8</f>
+        <f t="shared" si="5"/>
         <v>0.92104559023504595</v>
       </c>
       <c r="F34" s="2">
-        <f>F8</f>
+        <f t="shared" si="5"/>
         <v>0.69470880820399195</v>
       </c>
       <c r="G34" s="2">
-        <f>G8</f>
+        <f t="shared" si="5"/>
         <v>0.65259499157233103</v>
       </c>
       <c r="H34" s="2">
-        <f>H8</f>
+        <f t="shared" si="5"/>
         <v>1.11666666666666</v>
       </c>
       <c r="I34" s="1">
-        <f>I8</f>
+        <f t="shared" si="5"/>
         <v>5.9639432635513898E-2</v>
       </c>
       <c r="J34" s="1">
-        <f>J8</f>
+        <f t="shared" si="5"/>
         <v>6.0089927606266198E-2</v>
       </c>
     </row>
@@ -2432,31 +3033,31 @@
         <v>0.153679610448271</v>
       </c>
       <c r="D37" s="3">
-        <f t="shared" ref="D37:J37" si="2">D3</f>
+        <f t="shared" ref="D37:J37" si="6">D3</f>
         <v>0.32052495709975298</v>
       </c>
       <c r="E37" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0.67738862149364099</v>
       </c>
       <c r="F37" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0.72312962730627905</v>
       </c>
       <c r="G37" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0.65262018332211302</v>
       </c>
       <c r="H37" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="I37" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>4.7924826086253897E-2</v>
       </c>
       <c r="J37" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>3.9585073275757901E-2</v>
       </c>
     </row>
@@ -2470,35 +3071,35 @@
         <v>ESM1-2-LR_SSP245_constVolc</v>
       </c>
       <c r="C38" s="3">
-        <f t="shared" ref="C38:J38" si="3">C5</f>
+        <f t="shared" ref="C38:J38" si="7">C5</f>
         <v>0.32272305160293702</v>
       </c>
       <c r="D38" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0.60963225535908305</v>
       </c>
       <c r="E38" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0.92550530731992098</v>
       </c>
       <c r="F38" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0.71242307999963705</v>
       </c>
       <c r="G38" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0.61013150635878699</v>
       </c>
       <c r="H38" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="I38" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>5.14577615073573E-2</v>
       </c>
       <c r="J38" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>3.9952145868938999E-2</v>
       </c>
     </row>
@@ -2516,31 +3117,31 @@
         <v>0.16500835590663099</v>
       </c>
       <c r="D39" s="3">
-        <f t="shared" ref="D39:J39" si="4">D7</f>
+        <f t="shared" ref="D39:J39" si="8">D7</f>
         <v>0.34150036785639698</v>
       </c>
       <c r="E39" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0.82410366011376901</v>
       </c>
       <c r="F39" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0.75525220045584596</v>
       </c>
       <c r="G39" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0.65528228338484396</v>
       </c>
       <c r="H39" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="I39" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>6.8233767139105395E-2</v>
       </c>
       <c r="J39" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>5.7310887082711301E-2</v>
       </c>
     </row>
@@ -2554,35 +3155,35 @@
         <v>NorESM_RCP45_VolcConst</v>
       </c>
       <c r="C40" s="3">
-        <f>C11</f>
+        <f t="shared" ref="C40:J40" si="9">C11</f>
         <v>0.34149028921088098</v>
       </c>
       <c r="D40" s="3">
-        <f>D11</f>
+        <f t="shared" si="9"/>
         <v>0.63497038219064394</v>
       </c>
       <c r="E40" s="3">
-        <f>E11</f>
+        <f t="shared" si="9"/>
         <v>0.9887736478686</v>
       </c>
       <c r="F40" s="2">
-        <f>F11</f>
+        <f t="shared" si="9"/>
         <v>0.73298331626506696</v>
       </c>
       <c r="G40" s="2">
-        <f>G11</f>
+        <f t="shared" si="9"/>
         <v>0.67448595360081598</v>
       </c>
       <c r="H40" s="2">
-        <f>H11</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="I40" s="1">
-        <f>I11</f>
+        <f t="shared" si="9"/>
         <v>4.7962799242892498E-2</v>
       </c>
       <c r="J40" s="1">
-        <f>J11</f>
+        <f t="shared" si="9"/>
         <v>4.2451274264061201E-2</v>
       </c>
     </row>
@@ -2596,35 +3197,35 @@
         <v>NorESM_RCP45_Volc</v>
       </c>
       <c r="C41" s="3">
-        <f>C9</f>
+        <f t="shared" ref="C41:J41" si="10">C9</f>
         <v>0.24172655046852501</v>
       </c>
       <c r="D41" s="3">
-        <f>D9</f>
+        <f t="shared" si="10"/>
         <v>0.45951717349270299</v>
       </c>
       <c r="E41" s="3">
-        <f>E9</f>
+        <f t="shared" si="10"/>
         <v>0.84197272967619696</v>
       </c>
       <c r="F41" s="2">
-        <f>F9</f>
+        <f t="shared" si="10"/>
         <v>0.78885052339075301</v>
       </c>
       <c r="G41" s="2">
-        <f>G9</f>
+        <f t="shared" si="10"/>
         <v>0.73038928215626897</v>
       </c>
       <c r="H41" s="2">
-        <f>H9</f>
+        <f t="shared" si="10"/>
         <v>1.05</v>
       </c>
       <c r="I41" s="1">
-        <f>I9</f>
+        <f t="shared" si="10"/>
         <v>6.00693062685295E-2</v>
       </c>
       <c r="J41" s="1">
-        <f>J9</f>
+        <f t="shared" si="10"/>
         <v>5.5749640580537503E-2</v>
       </c>
     </row>
@@ -2632,4 +3233,1456 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39687A6D-F203-8948-835B-1E2A48CE7160}">
+  <dimension ref="A1:J43"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B1" s="7"/>
+      <c r="C1" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J1" s="7"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B2" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B3" s="7"/>
+      <c r="C3" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" t="str">
+        <f>[1]final_combined_7methods_wide_ff!A$7</f>
+        <v>fut_ESM1-2-LR_SSP370_constVolc</v>
+      </c>
+      <c r="B4" s="7" t="str">
+        <f>RIGHT(A4,LEN(A4)-4)</f>
+        <v>ESM1-2-LR_SSP370_constVolc</v>
+      </c>
+      <c r="C4" s="8">
+        <f>[1]final_combined_7methods_wide_ff!C$7</f>
+        <v>0.54619910490746704</v>
+      </c>
+      <c r="D4" s="8">
+        <f>[1]final_combined_7methods_wide_ff!D$7</f>
+        <v>0.85026964875689004</v>
+      </c>
+      <c r="E4" s="8">
+        <f>[1]final_combined_7methods_wide_ff!E$7</f>
+        <v>0.99999836434091705</v>
+      </c>
+      <c r="F4" s="9">
+        <f>[1]final_combined_7methods_wide_ff!F$7</f>
+        <v>0.35236140573901098</v>
+      </c>
+      <c r="G4" s="9">
+        <f>[1]final_combined_7methods_wide_ff!G$7</f>
+        <v>0.27106817338542499</v>
+      </c>
+      <c r="H4" s="9">
+        <f>[1]final_combined_7methods_wide_ff!H$7</f>
+        <v>1.08</v>
+      </c>
+      <c r="I4" s="10">
+        <f>[1]final_combined_7methods_wide_ff!I$7</f>
+        <v>3.67655115767027E-2</v>
+      </c>
+      <c r="J4" s="10">
+        <f>[1]final_combined_7methods_wide_ff!J$7</f>
+        <v>3.35054597998811E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" t="str">
+        <f>[1]final_combined_7methods_wide_ff!A$5</f>
+        <v>fut_ESM1-2-LR_SSP245_constVolc</v>
+      </c>
+      <c r="B5" s="7" t="str">
+        <f t="shared" ref="B5:B15" si="0">RIGHT(A5,LEN(A5)-4)</f>
+        <v>ESM1-2-LR_SSP245_constVolc</v>
+      </c>
+      <c r="C5" s="8">
+        <f>[1]final_combined_7methods_wide_ff!C$5</f>
+        <v>0.55693243562445705</v>
+      </c>
+      <c r="D5" s="8">
+        <f>[1]final_combined_7methods_wide_ff!D$5</f>
+        <v>0.85137216343120803</v>
+      </c>
+      <c r="E5" s="8">
+        <f>[1]final_combined_7methods_wide_ff!E$5</f>
+        <v>0.99159617730083804</v>
+      </c>
+      <c r="F5" s="9">
+        <f>[1]final_combined_7methods_wide_ff!F$5</f>
+        <v>0.48770586775952401</v>
+      </c>
+      <c r="G5" s="9">
+        <f>[1]final_combined_7methods_wide_ff!G$5</f>
+        <v>0.48135376341167602</v>
+      </c>
+      <c r="H5" s="9">
+        <f>[1]final_combined_7methods_wide_ff!H$5</f>
+        <v>1.04</v>
+      </c>
+      <c r="I5" s="10">
+        <f>[1]final_combined_7methods_wide_ff!I$5</f>
+        <v>3.2207269952229799E-2</v>
+      </c>
+      <c r="J5" s="10">
+        <f>[1]final_combined_7methods_wide_ff!J$5</f>
+        <v>3.0085110989888701E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" t="str">
+        <f>[1]final_combined_7methods_wide_ff!A$3</f>
+        <v>fut_ESM1-2-LR_SSP126_constVolc</v>
+      </c>
+      <c r="B6" s="7" t="str">
+        <f>RIGHT(A6,LEN(A6)-4)</f>
+        <v>ESM1-2-LR_SSP126_constVolc</v>
+      </c>
+      <c r="C6" s="8">
+        <f>[1]final_combined_7methods_wide_ff!C$3</f>
+        <v>0.20755706849306199</v>
+      </c>
+      <c r="D6" s="8">
+        <f>[1]final_combined_7methods_wide_ff!D$3</f>
+        <v>0.39313285295950501</v>
+      </c>
+      <c r="E6" s="8">
+        <f>[1]final_combined_7methods_wide_ff!E$3</f>
+        <v>0.75508045533102697</v>
+      </c>
+      <c r="F6" s="9">
+        <f>[1]final_combined_7methods_wide_ff!F$3</f>
+        <v>0.56758655826126803</v>
+      </c>
+      <c r="G6" s="9">
+        <f>[1]final_combined_7methods_wide_ff!G$3</f>
+        <v>0.60241889512051305</v>
+      </c>
+      <c r="H6" s="9">
+        <f>[1]final_combined_7methods_wide_ff!H$3</f>
+        <v>1.46</v>
+      </c>
+      <c r="I6" s="10">
+        <f>[1]final_combined_7methods_wide_ff!I$3</f>
+        <v>3.55967136847853E-2</v>
+      </c>
+      <c r="J6" s="10">
+        <f>[1]final_combined_7methods_wide_ff!J$3</f>
+        <v>3.4755163366221101E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" t="str">
+        <f>[1]final_combined_7methods_wide_ff!A$11</f>
+        <v>fut_NorESM_RCP45_VolcConst</v>
+      </c>
+      <c r="B7" s="7" t="str">
+        <f>RIGHT(A7,LEN(A7)-4)</f>
+        <v>NorESM_RCP45_VolcConst</v>
+      </c>
+      <c r="C7" s="8">
+        <f>[1]final_combined_7methods_wide_ff!C$11</f>
+        <v>0.53338404346295398</v>
+      </c>
+      <c r="D7" s="8">
+        <f>[1]final_combined_7methods_wide_ff!D$11</f>
+        <v>0.87097082324211506</v>
+      </c>
+      <c r="E7" s="8">
+        <f>[1]final_combined_7methods_wide_ff!E$11</f>
+        <v>0.99999430169446302</v>
+      </c>
+      <c r="F7" s="9">
+        <f>[1]final_combined_7methods_wide_ff!F$11</f>
+        <v>0.59136052630917102</v>
+      </c>
+      <c r="G7" s="9">
+        <f>[1]final_combined_7methods_wide_ff!G$11</f>
+        <v>0.62348162834786303</v>
+      </c>
+      <c r="H7" s="9">
+        <f>[1]final_combined_7methods_wide_ff!H$11</f>
+        <v>1.0166666666666599</v>
+      </c>
+      <c r="I7" s="10">
+        <f>[1]final_combined_7methods_wide_ff!I$11</f>
+        <v>3.00118195904426E-2</v>
+      </c>
+      <c r="J7" s="10">
+        <f>[1]final_combined_7methods_wide_ff!J$11</f>
+        <v>3.0029336713997799E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" t="str">
+        <f>[1]final_combined_7methods_wide_ff!A$9</f>
+        <v>fut_NorESM_RCP45_Volc</v>
+      </c>
+      <c r="B8" s="7" t="str">
+        <f>RIGHT(A8,LEN(A8)-4)</f>
+        <v>NorESM_RCP45_Volc</v>
+      </c>
+      <c r="C8" s="8">
+        <f>[1]final_combined_7methods_wide_ff!C$9</f>
+        <v>0.295802697172452</v>
+      </c>
+      <c r="D8" s="8">
+        <f>[1]final_combined_7methods_wide_ff!D$9</f>
+        <v>0.54277920035025196</v>
+      </c>
+      <c r="E8" s="8">
+        <f>[1]final_combined_7methods_wide_ff!E$9</f>
+        <v>0.87879965089157297</v>
+      </c>
+      <c r="F8" s="9">
+        <f>[1]final_combined_7methods_wide_ff!F$9</f>
+        <v>0.71051840812753497</v>
+      </c>
+      <c r="G8" s="9">
+        <f>[1]final_combined_7methods_wide_ff!G$9</f>
+        <v>0.77054138023377905</v>
+      </c>
+      <c r="H8" s="9">
+        <f>[1]final_combined_7methods_wide_ff!H$9</f>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="I8" s="10">
+        <f>[1]final_combined_7methods_wide_ff!I$9</f>
+        <v>4.9516240832959101E-2</v>
+      </c>
+      <c r="J8" s="10">
+        <f>[1]final_combined_7methods_wide_ff!J$9</f>
+        <v>5.1047676785816301E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11" t="str">
+        <f>[2]final_combined_16methods_wide_f!A$7</f>
+        <v>fut_ESM1-2-LR_SSP370_constVolc</v>
+      </c>
+      <c r="B11" s="7" t="str">
+        <f>RIGHT(A11,LEN(A11)-4)</f>
+        <v>ESM1-2-LR_SSP370_constVolc</v>
+      </c>
+      <c r="C11" s="8">
+        <f>[2]final_combined_16methods_wide_f!C$7</f>
+        <v>0.55738744535778695</v>
+      </c>
+      <c r="D11" s="8">
+        <f>[2]final_combined_16methods_wide_f!D$7</f>
+        <v>0.85120073146078801</v>
+      </c>
+      <c r="E11" s="8">
+        <f>[2]final_combined_16methods_wide_f!E$7</f>
+        <v>0.99999778206774803</v>
+      </c>
+      <c r="F11" s="9">
+        <f>[2]final_combined_16methods_wide_f!F$7</f>
+        <v>0.34517946300421798</v>
+      </c>
+      <c r="G11" s="9">
+        <f>[2]final_combined_16methods_wide_f!G$7</f>
+        <v>0.26883137024650899</v>
+      </c>
+      <c r="H11" s="9">
+        <f>[2]final_combined_16methods_wide_f!H$7</f>
+        <v>1.06</v>
+      </c>
+      <c r="I11" s="10">
+        <f>[2]final_combined_16methods_wide_f!I$7</f>
+        <v>3.6506341264737098E-2</v>
+      </c>
+      <c r="J11" s="10">
+        <f>[2]final_combined_16methods_wide_f!J$7</f>
+        <v>3.3248760486993302E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12" t="str">
+        <f>[2]final_combined_16methods_wide_f!A$5</f>
+        <v>fut_ESM1-2-LR_SSP245_constVolc</v>
+      </c>
+      <c r="B12" s="7" t="str">
+        <f>RIGHT(A12,LEN(A12)-4)</f>
+        <v>ESM1-2-LR_SSP245_constVolc</v>
+      </c>
+      <c r="C12" s="8">
+        <f>[2]final_combined_16methods_wide_f!C$5</f>
+        <v>0.55327213342940795</v>
+      </c>
+      <c r="D12" s="8">
+        <f>[2]final_combined_16methods_wide_f!D$5</f>
+        <v>0.83542228277474595</v>
+      </c>
+      <c r="E12" s="8">
+        <f>[2]final_combined_16methods_wide_f!E$5</f>
+        <v>0.99065301016602703</v>
+      </c>
+      <c r="F12" s="9">
+        <f>[2]final_combined_16methods_wide_f!F$5</f>
+        <v>0.474326788739316</v>
+      </c>
+      <c r="G12" s="9">
+        <f>[2]final_combined_16methods_wide_f!G$5</f>
+        <v>0.46525764271050302</v>
+      </c>
+      <c r="H12" s="9">
+        <f>[2]final_combined_16methods_wide_f!H$5</f>
+        <v>1.08</v>
+      </c>
+      <c r="I12" s="10">
+        <f>[2]final_combined_16methods_wide_f!I$5</f>
+        <v>3.2244062898479302E-2</v>
+      </c>
+      <c r="J12" s="10">
+        <f>[2]final_combined_16methods_wide_f!J$5</f>
+        <v>3.00446004526808E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" t="str">
+        <f>[2]final_combined_16methods_wide_f!A$3</f>
+        <v>fut_ESM1-2-LR_SSP126_constVolc</v>
+      </c>
+      <c r="B13" s="7" t="str">
+        <f>RIGHT(A13,LEN(A13)-4)</f>
+        <v>ESM1-2-LR_SSP126_constVolc</v>
+      </c>
+      <c r="C13" s="8">
+        <f>[2]final_combined_16methods_wide_f!C$3</f>
+        <v>0.20576812891627</v>
+      </c>
+      <c r="D13" s="8">
+        <f>[2]final_combined_16methods_wide_f!D$3</f>
+        <v>0.39131798477193203</v>
+      </c>
+      <c r="E13" s="8">
+        <f>[2]final_combined_16methods_wide_f!E$3</f>
+        <v>0.75985380247993595</v>
+      </c>
+      <c r="F13" s="9">
+        <f>[2]final_combined_16methods_wide_f!F$3</f>
+        <v>0.555132277466724</v>
+      </c>
+      <c r="G13" s="9">
+        <f>[2]final_combined_16methods_wide_f!G$3</f>
+        <v>0.58900071435593904</v>
+      </c>
+      <c r="H13" s="9">
+        <f>[2]final_combined_16methods_wide_f!H$3</f>
+        <v>1.32</v>
+      </c>
+      <c r="I13" s="10">
+        <f>[2]final_combined_16methods_wide_f!I$3</f>
+        <v>3.5373468407243903E-2</v>
+      </c>
+      <c r="J13" s="10">
+        <f>[2]final_combined_16methods_wide_f!J$3</f>
+        <v>3.4498382156762097E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14" t="str">
+        <f>[2]final_combined_16methods_wide_f!A$11</f>
+        <v>fut_NorESM_RCP45_VolcConst</v>
+      </c>
+      <c r="B14" s="7" t="str">
+        <f>RIGHT(A14,LEN(A14)-4)</f>
+        <v>NorESM_RCP45_VolcConst</v>
+      </c>
+      <c r="C14" s="8">
+        <f>[2]final_combined_16methods_wide_f!C$11</f>
+        <v>0.53542936181767697</v>
+      </c>
+      <c r="D14" s="8">
+        <f>[2]final_combined_16methods_wide_f!D$11</f>
+        <v>0.86675058660220505</v>
+      </c>
+      <c r="E14" s="8">
+        <f>[2]final_combined_16methods_wide_f!E$11</f>
+        <v>0.99999826488588195</v>
+      </c>
+      <c r="F14" s="9">
+        <f>[2]final_combined_16methods_wide_f!F$11</f>
+        <v>0.56829985226404101</v>
+      </c>
+      <c r="G14" s="9">
+        <f>[2]final_combined_16methods_wide_f!G$11</f>
+        <v>0.47488218559303003</v>
+      </c>
+      <c r="H14" s="9">
+        <f>[2]final_combined_16methods_wide_f!H$11</f>
+        <v>1.0166666666666599</v>
+      </c>
+      <c r="I14" s="10">
+        <f>[2]final_combined_16methods_wide_f!I$11</f>
+        <v>2.9692821763125501E-2</v>
+      </c>
+      <c r="J14" s="10">
+        <f>[2]final_combined_16methods_wide_f!J$11</f>
+        <v>2.9527986662152901E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15" t="str">
+        <f>[2]final_combined_16methods_wide_f!A$9</f>
+        <v>fut_NorESM_RCP45_Volc</v>
+      </c>
+      <c r="B15" s="7" t="str">
+        <f>RIGHT(A15,LEN(A15)-4)</f>
+        <v>NorESM_RCP45_Volc</v>
+      </c>
+      <c r="C15" s="8">
+        <f>[2]final_combined_16methods_wide_f!C$9</f>
+        <v>0.30106359931930998</v>
+      </c>
+      <c r="D15" s="8">
+        <f>[2]final_combined_16methods_wide_f!D$9</f>
+        <v>0.55168877761303903</v>
+      </c>
+      <c r="E15" s="8">
+        <f>[2]final_combined_16methods_wide_f!E$9</f>
+        <v>0.88473982556344</v>
+      </c>
+      <c r="F15" s="9">
+        <f>[2]final_combined_16methods_wide_f!F$9</f>
+        <v>0.72122719204056196</v>
+      </c>
+      <c r="G15" s="9">
+        <f>[2]final_combined_16methods_wide_f!G$9</f>
+        <v>0.71024730946443604</v>
+      </c>
+      <c r="H15" s="9">
+        <f>[2]final_combined_16methods_wide_f!H$9</f>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="I15" s="10">
+        <f>[2]final_combined_16methods_wide_f!I$9</f>
+        <v>4.91660796604797E-2</v>
+      </c>
+      <c r="J15" s="10">
+        <f>[2]final_combined_16methods_wide_f!J$9</f>
+        <v>5.0769616326947098E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B17" s="7"/>
+      <c r="C17" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A18" t="str">
+        <f>[2]final_combined_16methods_wide_f!A$7</f>
+        <v>fut_ESM1-2-LR_SSP370_constVolc</v>
+      </c>
+      <c r="B18" s="7" t="str">
+        <f>RIGHT(A18,LEN(A18)-4)</f>
+        <v>ESM1-2-LR_SSP370_constVolc</v>
+      </c>
+      <c r="C18" s="8">
+        <f>[3]final_combined_32methods_wide_f!C$7</f>
+        <v>0.54447939616679597</v>
+      </c>
+      <c r="D18" s="8">
+        <f>[3]final_combined_32methods_wide_f!D$7</f>
+        <v>0.84570767317965201</v>
+      </c>
+      <c r="E18" s="8">
+        <f>[3]final_combined_32methods_wide_f!E$7</f>
+        <v>0.99999336318933896</v>
+      </c>
+      <c r="F18" s="9">
+        <f>[3]final_combined_32methods_wide_f!F$7</f>
+        <v>0.35570970869045898</v>
+      </c>
+      <c r="G18" s="9">
+        <f>[3]final_combined_32methods_wide_f!G$7</f>
+        <v>0.27231278148992299</v>
+      </c>
+      <c r="H18" s="9">
+        <f>[3]final_combined_32methods_wide_f!H$7</f>
+        <v>1.06</v>
+      </c>
+      <c r="I18" s="10">
+        <f>[3]final_combined_32methods_wide_f!I$7</f>
+        <v>3.7020164041822297E-2</v>
+      </c>
+      <c r="J18" s="10">
+        <f>[3]final_combined_32methods_wide_f!J$7</f>
+        <v>3.3484937846857799E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A19" t="str">
+        <f>[2]final_combined_16methods_wide_f!A$5</f>
+        <v>fut_ESM1-2-LR_SSP245_constVolc</v>
+      </c>
+      <c r="B19" s="7" t="str">
+        <f>RIGHT(A19,LEN(A19)-4)</f>
+        <v>ESM1-2-LR_SSP245_constVolc</v>
+      </c>
+      <c r="C19" s="8">
+        <f>[3]final_combined_32methods_wide_f!C$5</f>
+        <v>0.53795071414849205</v>
+      </c>
+      <c r="D19" s="8">
+        <f>[3]final_combined_32methods_wide_f!D$5</f>
+        <v>0.82966165685017401</v>
+      </c>
+      <c r="E19" s="8">
+        <f>[3]final_combined_32methods_wide_f!E$5</f>
+        <v>0.99279793965561802</v>
+      </c>
+      <c r="F19" s="9">
+        <f>[3]final_combined_32methods_wide_f!F$5</f>
+        <v>0.47296562334456499</v>
+      </c>
+      <c r="G19" s="9">
+        <f>[3]final_combined_32methods_wide_f!G$5</f>
+        <v>0.46616316879048197</v>
+      </c>
+      <c r="H19" s="9">
+        <f>[3]final_combined_32methods_wide_f!H$5</f>
+        <v>1.06</v>
+      </c>
+      <c r="I19" s="10">
+        <f>[3]final_combined_32methods_wide_f!I$5</f>
+        <v>3.1879531639024898E-2</v>
+      </c>
+      <c r="J19" s="10">
+        <f>[3]final_combined_32methods_wide_f!J$5</f>
+        <v>2.9940485328590699E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A20" t="str">
+        <f>[2]final_combined_16methods_wide_f!A$3</f>
+        <v>fut_ESM1-2-LR_SSP126_constVolc</v>
+      </c>
+      <c r="B20" s="7" t="str">
+        <f>RIGHT(A20,LEN(A20)-4)</f>
+        <v>ESM1-2-LR_SSP126_constVolc</v>
+      </c>
+      <c r="C20" s="8">
+        <f>[3]final_combined_32methods_wide_f!C$3</f>
+        <v>0.21789558676590701</v>
+      </c>
+      <c r="D20" s="8">
+        <f>[3]final_combined_32methods_wide_f!D$3</f>
+        <v>0.41545942039553602</v>
+      </c>
+      <c r="E20" s="8">
+        <f>[3]final_combined_32methods_wide_f!E$3</f>
+        <v>0.79430186547134896</v>
+      </c>
+      <c r="F20" s="9">
+        <f>[3]final_combined_32methods_wide_f!F$3</f>
+        <v>0.55355925523003502</v>
+      </c>
+      <c r="G20" s="9">
+        <f>[3]final_combined_32methods_wide_f!G$3</f>
+        <v>0.58926144099300404</v>
+      </c>
+      <c r="H20" s="9">
+        <f>[3]final_combined_32methods_wide_f!H$3</f>
+        <v>1.32</v>
+      </c>
+      <c r="I20" s="10">
+        <f>[3]final_combined_32methods_wide_f!I$3</f>
+        <v>3.4759033290035199E-2</v>
+      </c>
+      <c r="J20" s="10">
+        <f>[3]final_combined_32methods_wide_f!J$3</f>
+        <v>3.4058045419036002E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A21" t="str">
+        <f>[2]final_combined_16methods_wide_f!A$11</f>
+        <v>fut_NorESM_RCP45_VolcConst</v>
+      </c>
+      <c r="B21" s="7" t="str">
+        <f>RIGHT(A21,LEN(A21)-4)</f>
+        <v>NorESM_RCP45_VolcConst</v>
+      </c>
+      <c r="C21" s="8">
+        <f>[3]final_combined_32methods_wide_f!C$11</f>
+        <v>0.54497070338604503</v>
+      </c>
+      <c r="D21" s="8">
+        <f>[3]final_combined_32methods_wide_f!D$11</f>
+        <v>0.869225259621072</v>
+      </c>
+      <c r="E21" s="8">
+        <f>[3]final_combined_32methods_wide_f!E$11</f>
+        <v>0.99999968353572399</v>
+      </c>
+      <c r="F21" s="9">
+        <f>[3]final_combined_32methods_wide_f!F$11</f>
+        <v>0.57234286872200302</v>
+      </c>
+      <c r="G21" s="9">
+        <f>[3]final_combined_32methods_wide_f!G$11</f>
+        <v>0.59778528724644397</v>
+      </c>
+      <c r="H21" s="9">
+        <f>[3]final_combined_32methods_wide_f!H$11</f>
+        <v>1.0166666666666599</v>
+      </c>
+      <c r="I21" s="10">
+        <f>[3]final_combined_32methods_wide_f!I$11</f>
+        <v>2.9416336109457701E-2</v>
+      </c>
+      <c r="J21" s="10">
+        <f>[3]final_combined_32methods_wide_f!J$11</f>
+        <v>2.9317239210130901E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A22" t="str">
+        <f>[2]final_combined_16methods_wide_f!A$9</f>
+        <v>fut_NorESM_RCP45_Volc</v>
+      </c>
+      <c r="B22" s="7" t="str">
+        <f>RIGHT(A22,LEN(A22)-4)</f>
+        <v>NorESM_RCP45_Volc</v>
+      </c>
+      <c r="C22" s="8">
+        <f>[3]final_combined_32methods_wide_f!C$9</f>
+        <v>0.32645120923792798</v>
+      </c>
+      <c r="D22" s="8">
+        <f>[3]final_combined_32methods_wide_f!D$9</f>
+        <v>0.59079979067163901</v>
+      </c>
+      <c r="E22" s="8">
+        <f>[3]final_combined_32methods_wide_f!E$9</f>
+        <v>0.90896191913690905</v>
+      </c>
+      <c r="F22" s="9">
+        <f>[3]final_combined_32methods_wide_f!F$9</f>
+        <v>0.73645404524055702</v>
+      </c>
+      <c r="G22" s="9">
+        <f>[3]final_combined_32methods_wide_f!G$9</f>
+        <v>0.81387864681549205</v>
+      </c>
+      <c r="H22" s="9">
+        <f>[3]final_combined_32methods_wide_f!H$9</f>
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="I22" s="10">
+        <f>[3]final_combined_32methods_wide_f!I$9</f>
+        <v>4.8982929865659303E-2</v>
+      </c>
+      <c r="J22" s="10">
+        <f>[3]final_combined_32methods_wide_f!J$9</f>
+        <v>5.0659588379776799E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="10"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B24" s="7"/>
+      <c r="C24" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A25" t="str">
+        <f>[1]final_combined_7methods_wide_ff!A$2</f>
+        <v>fut_ESM1-2-LR_SSP126_constVolc</v>
+      </c>
+      <c r="B25" s="7" t="str">
+        <f t="shared" ref="B25:B29" si="1">RIGHT(A25,LEN(A25)-4)</f>
+        <v>ESM1-2-LR_SSP126_constVolc</v>
+      </c>
+      <c r="C25" s="8">
+        <f>[1]final_combined_7methods_wide_ff!C$2</f>
+        <v>0.21132096210941201</v>
+      </c>
+      <c r="D25" s="8">
+        <f>[1]final_combined_7methods_wide_ff!D$2</f>
+        <v>0.39883056449283</v>
+      </c>
+      <c r="E25" s="8">
+        <f>[1]final_combined_7methods_wide_ff!E$2</f>
+        <v>0.74598077875606195</v>
+      </c>
+      <c r="F25" s="9">
+        <f>[1]final_combined_7methods_wide_ff!F$2</f>
+        <v>0.528912270279561</v>
+      </c>
+      <c r="G25" s="9">
+        <f>[1]final_combined_7methods_wide_ff!G$2</f>
+        <v>0.577668141911305</v>
+      </c>
+      <c r="H25" s="9">
+        <f>[1]final_combined_7methods_wide_ff!H$2</f>
+        <v>1.42</v>
+      </c>
+      <c r="I25" s="10">
+        <f>[1]final_combined_7methods_wide_ff!I$2</f>
+        <v>3.8089126961787199E-2</v>
+      </c>
+      <c r="J25" s="10">
+        <f>[1]final_combined_7methods_wide_ff!J$2</f>
+        <v>3.8257160319207201E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A26" t="str">
+        <f>[1]final_combined_7methods_wide_ff!A$4</f>
+        <v>fut_ESM1-2-LR_SSP245_constVolc</v>
+      </c>
+      <c r="B26" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>ESM1-2-LR_SSP245_constVolc</v>
+      </c>
+      <c r="C26" s="8">
+        <f>[1]final_combined_7methods_wide_ff!C$4</f>
+        <v>0.51324464439026996</v>
+      </c>
+      <c r="D26" s="8">
+        <f>[1]final_combined_7methods_wide_ff!D$4</f>
+        <v>0.80791569847865796</v>
+      </c>
+      <c r="E26" s="8">
+        <f>[1]final_combined_7methods_wide_ff!E$4</f>
+        <v>0.98599074521400898</v>
+      </c>
+      <c r="F26" s="9">
+        <f>[1]final_combined_7methods_wide_ff!F$4</f>
+        <v>0.40375019023063502</v>
+      </c>
+      <c r="G26" s="9">
+        <f>[1]final_combined_7methods_wide_ff!G$4</f>
+        <v>0.409028023352207</v>
+      </c>
+      <c r="H26" s="9">
+        <f>[1]final_combined_7methods_wide_ff!H$4</f>
+        <v>1.04</v>
+      </c>
+      <c r="I26" s="10">
+        <f>[1]final_combined_7methods_wide_ff!I$4</f>
+        <v>3.5707271533879398E-2</v>
+      </c>
+      <c r="J26" s="10">
+        <f>[1]final_combined_7methods_wide_ff!J$4</f>
+        <v>3.4964253761786197E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A27" t="str">
+        <f>[1]final_combined_7methods_wide_ff!A$6</f>
+        <v>fut_ESM1-2-LR_SSP370_constVolc</v>
+      </c>
+      <c r="B27" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>ESM1-2-LR_SSP370_constVolc</v>
+      </c>
+      <c r="C27" s="8">
+        <f>[1]final_combined_7methods_wide_ff!C$6</f>
+        <v>0.56326546202472005</v>
+      </c>
+      <c r="D27" s="8">
+        <f>[1]final_combined_7methods_wide_ff!D$6</f>
+        <v>0.85916848777764898</v>
+      </c>
+      <c r="E27" s="8">
+        <f>[1]final_combined_7methods_wide_ff!E$6</f>
+        <v>0.99999972101326395</v>
+      </c>
+      <c r="F27" s="9">
+        <f>[1]final_combined_7methods_wide_ff!F$6</f>
+        <v>0.28103151374638402</v>
+      </c>
+      <c r="G27" s="9">
+        <f>[1]final_combined_7methods_wide_ff!G$6</f>
+        <v>0.21456750872458</v>
+      </c>
+      <c r="H27" s="9">
+        <f>[1]final_combined_7methods_wide_ff!H$6</f>
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="I27" s="10">
+        <f>[1]final_combined_7methods_wide_ff!I$6</f>
+        <v>3.5110423411378301E-2</v>
+      </c>
+      <c r="J27" s="10">
+        <f>[1]final_combined_7methods_wide_ff!J$6</f>
+        <v>3.1880713374243502E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A28" t="str">
+        <f>[1]final_combined_7methods_wide_ff!A$8</f>
+        <v>fut_NorESM_RCP45_Volc</v>
+      </c>
+      <c r="B28" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>NorESM_RCP45_Volc</v>
+      </c>
+      <c r="C28" s="8">
+        <f>[1]final_combined_7methods_wide_ff!C$8</f>
+        <v>0.307948440316553</v>
+      </c>
+      <c r="D28" s="8">
+        <f>[1]final_combined_7methods_wide_ff!D$8</f>
+        <v>0.56086887661448304</v>
+      </c>
+      <c r="E28" s="8">
+        <f>[1]final_combined_7methods_wide_ff!E$8</f>
+        <v>0.88328191599981898</v>
+      </c>
+      <c r="F28" s="9">
+        <f>[1]final_combined_7methods_wide_ff!F$8</f>
+        <v>0.68845574872436999</v>
+      </c>
+      <c r="G28" s="9">
+        <f>[1]final_combined_7methods_wide_ff!G$8</f>
+        <v>0.73625220438107497</v>
+      </c>
+      <c r="H28" s="9">
+        <f>[1]final_combined_7methods_wide_ff!H$8</f>
+        <v>1.11666666666666</v>
+      </c>
+      <c r="I28" s="10">
+        <f>[1]final_combined_7methods_wide_ff!I$8</f>
+        <v>5.2707464159806802E-2</v>
+      </c>
+      <c r="J28" s="10">
+        <f>[1]final_combined_7methods_wide_ff!J$8</f>
+        <v>5.4510865770008098E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A29" t="str">
+        <f>[1]final_combined_7methods_wide_ff!A$10</f>
+        <v>fut_NorESM_RCP45_VolcConst</v>
+      </c>
+      <c r="B29" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>NorESM_RCP45_VolcConst</v>
+      </c>
+      <c r="C29" s="8">
+        <f>[1]final_combined_7methods_wide_ff!C$10</f>
+        <v>0.54514943518981696</v>
+      </c>
+      <c r="D29" s="8">
+        <f>[1]final_combined_7methods_wide_ff!D$10</f>
+        <v>0.87461617266192504</v>
+      </c>
+      <c r="E29" s="8">
+        <f>[1]final_combined_7methods_wide_ff!E$10</f>
+        <v>0.99999951520399999</v>
+      </c>
+      <c r="F29" s="9">
+        <f>[1]final_combined_7methods_wide_ff!F$10</f>
+        <v>0.43700824798559201</v>
+      </c>
+      <c r="G29" s="9">
+        <f>[1]final_combined_7methods_wide_ff!G$10</f>
+        <v>0.46820692982842599</v>
+      </c>
+      <c r="H29" s="9">
+        <f>[1]final_combined_7methods_wide_ff!H$10</f>
+        <v>1</v>
+      </c>
+      <c r="I29" s="10">
+        <f>[1]final_combined_7methods_wide_ff!I$10</f>
+        <v>3.0552993250828501E-2</v>
+      </c>
+      <c r="J29" s="10">
+        <f>[1]final_combined_7methods_wide_ff!J$10</f>
+        <v>3.1015313492675101E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="10"/>
+      <c r="J30" s="10"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B31" s="7"/>
+      <c r="C31" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="10"/>
+      <c r="J31" s="10"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A32" t="str">
+        <f>[2]final_combined_16methods_wide_f!A$2</f>
+        <v>fut_ESM1-2-LR_SSP126_constVolc</v>
+      </c>
+      <c r="B32" s="7" t="str">
+        <f>RIGHT(A32,LEN(A32)-4)</f>
+        <v>ESM1-2-LR_SSP126_constVolc</v>
+      </c>
+      <c r="C32" s="8">
+        <f>[2]final_combined_16methods_wide_f!C$2</f>
+        <v>0.21863766120108799</v>
+      </c>
+      <c r="D32" s="8">
+        <f>[2]final_combined_16methods_wide_f!D$2</f>
+        <v>0.41443677964713499</v>
+      </c>
+      <c r="E32" s="8">
+        <f>[2]final_combined_16methods_wide_f!E$2</f>
+        <v>0.77937568423139103</v>
+      </c>
+      <c r="F32" s="11">
+        <f>[2]final_combined_16methods_wide_f!F$2</f>
+        <v>0.48696744999126601</v>
+      </c>
+      <c r="G32" s="11">
+        <f>[2]final_combined_16methods_wide_f!G$2</f>
+        <v>0.51389146851774203</v>
+      </c>
+      <c r="H32" s="11">
+        <f>[2]final_combined_16methods_wide_f!H$2</f>
+        <v>1.32</v>
+      </c>
+      <c r="I32" s="10">
+        <f>[2]final_combined_16methods_wide_f!I$2</f>
+        <v>3.50856668376376E-2</v>
+      </c>
+      <c r="J32" s="10">
+        <f>[2]final_combined_16methods_wide_f!J$2</f>
+        <v>3.3615419242651802E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A33" t="str">
+        <f>[2]final_combined_16methods_wide_f!A$4</f>
+        <v>fut_ESM1-2-LR_SSP245_constVolc</v>
+      </c>
+      <c r="B33" s="7" t="str">
+        <f>RIGHT(A33,LEN(A33)-4)</f>
+        <v>ESM1-2-LR_SSP245_constVolc</v>
+      </c>
+      <c r="C33" s="8">
+        <f>[2]final_combined_16methods_wide_f!C$4</f>
+        <v>0.50241628034270402</v>
+      </c>
+      <c r="D33" s="8">
+        <f>[2]final_combined_16methods_wide_f!D$4</f>
+        <v>0.80083031539555205</v>
+      </c>
+      <c r="E33" s="8">
+        <f>[2]final_combined_16methods_wide_f!E$4</f>
+        <v>0.98233423425677902</v>
+      </c>
+      <c r="F33" s="11">
+        <f>[2]final_combined_16methods_wide_f!F$4</f>
+        <v>0.37766050566306703</v>
+      </c>
+      <c r="G33" s="11">
+        <f>[2]final_combined_16methods_wide_f!G$4</f>
+        <v>0.36062433239381603</v>
+      </c>
+      <c r="H33" s="11">
+        <f>[2]final_combined_16methods_wide_f!H$4</f>
+        <v>1.04</v>
+      </c>
+      <c r="I33" s="10">
+        <f>[2]final_combined_16methods_wide_f!I$4</f>
+        <v>3.3762834915676602E-2</v>
+      </c>
+      <c r="J33" s="10">
+        <f>[2]final_combined_16methods_wide_f!J$4</f>
+        <v>3.1137489609733799E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A34" t="str">
+        <f>[2]final_combined_16methods_wide_f!A$6</f>
+        <v>fut_ESM1-2-LR_SSP370_constVolc</v>
+      </c>
+      <c r="B34" s="7" t="str">
+        <f>RIGHT(A34,LEN(A34)-4)</f>
+        <v>ESM1-2-LR_SSP370_constVolc</v>
+      </c>
+      <c r="C34" s="8">
+        <f>[2]final_combined_16methods_wide_f!C$6</f>
+        <v>0.53501465488853195</v>
+      </c>
+      <c r="D34" s="8">
+        <f>[2]final_combined_16methods_wide_f!D$6</f>
+        <v>0.84813894955111901</v>
+      </c>
+      <c r="E34" s="8">
+        <f>[2]final_combined_16methods_wide_f!E$6</f>
+        <v>0.99999924843690502</v>
+      </c>
+      <c r="F34" s="11">
+        <f>[2]final_combined_16methods_wide_f!F$6</f>
+        <v>0.30089129959560101</v>
+      </c>
+      <c r="G34" s="11">
+        <f>[2]final_combined_16methods_wide_f!G$6</f>
+        <v>0.205675254798835</v>
+      </c>
+      <c r="H34" s="11">
+        <f>[2]final_combined_16methods_wide_f!H$6</f>
+        <v>1.04</v>
+      </c>
+      <c r="I34" s="10">
+        <f>[2]final_combined_16methods_wide_f!I$6</f>
+        <v>3.6451904631969602E-2</v>
+      </c>
+      <c r="J34" s="10">
+        <f>[2]final_combined_16methods_wide_f!J$6</f>
+        <v>3.0872821507860401E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A35" t="str">
+        <f>[2]final_combined_16methods_wide_f!A$8</f>
+        <v>fut_NorESM_RCP45_Volc</v>
+      </c>
+      <c r="B35" s="7" t="str">
+        <f>RIGHT(A35,LEN(A35)-4)</f>
+        <v>NorESM_RCP45_Volc</v>
+      </c>
+      <c r="C35" s="8">
+        <f>[2]final_combined_16methods_wide_f!C$8</f>
+        <v>0.31140257165176499</v>
+      </c>
+      <c r="D35" s="8">
+        <f>[2]final_combined_16methods_wide_f!D$8</f>
+        <v>0.56608191326903601</v>
+      </c>
+      <c r="E35" s="8">
+        <f>[2]final_combined_16methods_wide_f!E$8</f>
+        <v>0.88269092438697105</v>
+      </c>
+      <c r="F35" s="11">
+        <f>[2]final_combined_16methods_wide_f!F$8</f>
+        <v>0.67277852547364903</v>
+      </c>
+      <c r="G35" s="11">
+        <f>[2]final_combined_16methods_wide_f!G$8</f>
+        <v>0.71152466033224304</v>
+      </c>
+      <c r="H35" s="11">
+        <f>[2]final_combined_16methods_wide_f!H$8</f>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="I35" s="10">
+        <f>[2]final_combined_16methods_wide_f!I$8</f>
+        <v>5.1493484708925202E-2</v>
+      </c>
+      <c r="J35" s="10">
+        <f>[2]final_combined_16methods_wide_f!J$8</f>
+        <v>5.2810633513484799E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A36" t="str">
+        <f>[2]final_combined_16methods_wide_f!A$10</f>
+        <v>fut_NorESM_RCP45_VolcConst</v>
+      </c>
+      <c r="B36" s="7" t="str">
+        <f>RIGHT(A36,LEN(A36)-4)</f>
+        <v>NorESM_RCP45_VolcConst</v>
+      </c>
+      <c r="C36" s="8">
+        <f>[2]final_combined_16methods_wide_f!C$10</f>
+        <v>0.54750981158324097</v>
+      </c>
+      <c r="D36" s="8">
+        <f>[2]final_combined_16methods_wide_f!D$10</f>
+        <v>0.87561068610950599</v>
+      </c>
+      <c r="E36" s="8">
+        <f>[2]final_combined_16methods_wide_f!E$10</f>
+        <v>0.99999991396280796</v>
+      </c>
+      <c r="F36" s="11">
+        <f>[2]final_combined_16methods_wide_f!F$10</f>
+        <v>0.42401791056917898</v>
+      </c>
+      <c r="G36" s="11">
+        <f>[2]final_combined_16methods_wide_f!G$10</f>
+        <v>0.44634031718390499</v>
+      </c>
+      <c r="H36" s="11">
+        <f>[2]final_combined_16methods_wide_f!H$10</f>
+        <v>1</v>
+      </c>
+      <c r="I36" s="10">
+        <f>[2]final_combined_16methods_wide_f!I$10</f>
+        <v>2.9801671950952201E-2</v>
+      </c>
+      <c r="J36" s="10">
+        <f>[2]final_combined_16methods_wide_f!J$10</f>
+        <v>2.94607743232577E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B37" s="7"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="10"/>
+      <c r="J37" s="10"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B38" s="7"/>
+      <c r="C38" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="10"/>
+      <c r="J38" s="10"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A39" t="str">
+        <f>[1]final_combined_7methods_wide_ff!A$2</f>
+        <v>fut_ESM1-2-LR_SSP126_constVolc</v>
+      </c>
+      <c r="B39" s="7" t="str">
+        <f t="shared" ref="B39:B43" si="2">RIGHT(A39,LEN(A39)-4)</f>
+        <v>ESM1-2-LR_SSP126_constVolc</v>
+      </c>
+      <c r="C39" s="8">
+        <f>[3]final_combined_32methods_wide_f!C$2</f>
+        <v>0.232929713919617</v>
+      </c>
+      <c r="D39" s="8">
+        <f>[3]final_combined_32methods_wide_f!D$2</f>
+        <v>0.437810418972361</v>
+      </c>
+      <c r="E39" s="8">
+        <f>[3]final_combined_32methods_wide_f!E$2</f>
+        <v>0.79678814890417904</v>
+      </c>
+      <c r="F39" s="9">
+        <f>[3]final_combined_32methods_wide_f!F$2</f>
+        <v>0.49141179481859698</v>
+      </c>
+      <c r="G39" s="9">
+        <f>[3]final_combined_32methods_wide_f!G$2</f>
+        <v>0.53467197927883603</v>
+      </c>
+      <c r="H39" s="9">
+        <f>[3]final_combined_32methods_wide_f!H$2</f>
+        <v>1.42</v>
+      </c>
+      <c r="I39" s="10">
+        <f>[3]final_combined_32methods_wide_f!I$2</f>
+        <v>3.5518948759835502E-2</v>
+      </c>
+      <c r="J39" s="10">
+        <f>[3]final_combined_32methods_wide_f!J$2</f>
+        <v>3.53737882916575E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A40" t="str">
+        <f>[1]final_combined_7methods_wide_ff!A$4</f>
+        <v>fut_ESM1-2-LR_SSP245_constVolc</v>
+      </c>
+      <c r="B40" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>ESM1-2-LR_SSP245_constVolc</v>
+      </c>
+      <c r="C40" s="8">
+        <f>[3]final_combined_32methods_wide_f!C$4</f>
+        <v>0.53099357414290005</v>
+      </c>
+      <c r="D40" s="8">
+        <f>[3]final_combined_32methods_wide_f!D$4</f>
+        <v>0.82487087083286303</v>
+      </c>
+      <c r="E40" s="8">
+        <f>[3]final_combined_32methods_wide_f!E$4</f>
+        <v>0.99032480491036301</v>
+      </c>
+      <c r="F40" s="9">
+        <f>[3]final_combined_32methods_wide_f!F$4</f>
+        <v>0.35769399037726202</v>
+      </c>
+      <c r="G40" s="9">
+        <f>[3]final_combined_32methods_wide_f!G$4</f>
+        <v>0.35330599421387099</v>
+      </c>
+      <c r="H40" s="9">
+        <f>[3]final_combined_32methods_wide_f!H$4</f>
+        <v>1.04</v>
+      </c>
+      <c r="I40" s="10">
+        <f>[3]final_combined_32methods_wide_f!I$4</f>
+        <v>3.2180212168593798E-2</v>
+      </c>
+      <c r="J40" s="10">
+        <f>[3]final_combined_32methods_wide_f!J$4</f>
+        <v>3.06081086701467E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A41" t="str">
+        <f>[1]final_combined_7methods_wide_ff!A$6</f>
+        <v>fut_ESM1-2-LR_SSP370_constVolc</v>
+      </c>
+      <c r="B41" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>ESM1-2-LR_SSP370_constVolc</v>
+      </c>
+      <c r="C41" s="8">
+        <f>[3]final_combined_32methods_wide_f!C$6</f>
+        <v>0.57071574749153098</v>
+      </c>
+      <c r="D41" s="8">
+        <f>[3]final_combined_32methods_wide_f!D$6</f>
+        <v>0.86860141429073801</v>
+      </c>
+      <c r="E41" s="8">
+        <f>[3]final_combined_32methods_wide_f!E$6</f>
+        <v>0.99999963584588902</v>
+      </c>
+      <c r="F41" s="9">
+        <f>[3]final_combined_32methods_wide_f!F$6</f>
+        <v>0.29445999120060601</v>
+      </c>
+      <c r="G41" s="9">
+        <f>[3]final_combined_32methods_wide_f!G$6</f>
+        <v>0.23833676480029001</v>
+      </c>
+      <c r="H41" s="9">
+        <f>[3]final_combined_32methods_wide_f!H$6</f>
+        <v>1.06</v>
+      </c>
+      <c r="I41" s="10">
+        <f>[3]final_combined_32methods_wide_f!I$6</f>
+        <v>3.58686394015027E-2</v>
+      </c>
+      <c r="J41" s="10">
+        <f>[3]final_combined_32methods_wide_f!J$6</f>
+        <v>3.3520742091611301E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A42" t="str">
+        <f>[1]final_combined_7methods_wide_ff!A$8</f>
+        <v>fut_NorESM_RCP45_Volc</v>
+      </c>
+      <c r="B42" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>NorESM_RCP45_Volc</v>
+      </c>
+      <c r="C42" s="8">
+        <f>[3]final_combined_32methods_wide_f!C$8</f>
+        <v>0.30728740459515103</v>
+      </c>
+      <c r="D42" s="8">
+        <f>[3]final_combined_32methods_wide_f!D$8</f>
+        <v>0.56063420527432195</v>
+      </c>
+      <c r="E42" s="8">
+        <f>[3]final_combined_32methods_wide_f!E$8</f>
+        <v>0.88528731731210597</v>
+      </c>
+      <c r="F42" s="9">
+        <f>[3]final_combined_32methods_wide_f!F$8</f>
+        <v>0.67512915843021004</v>
+      </c>
+      <c r="G42" s="9">
+        <f>[3]final_combined_32methods_wide_f!G$8</f>
+        <v>0.70899514228895699</v>
+      </c>
+      <c r="H42" s="9">
+        <f>[3]final_combined_32methods_wide_f!H$8</f>
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="I42" s="10">
+        <f>[3]final_combined_32methods_wide_f!I$8</f>
+        <v>5.1485888988200099E-2</v>
+      </c>
+      <c r="J42" s="10">
+        <f>[3]final_combined_32methods_wide_f!J$8</f>
+        <v>5.2533223607533798E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A43" t="str">
+        <f>[1]final_combined_7methods_wide_ff!A$10</f>
+        <v>fut_NorESM_RCP45_VolcConst</v>
+      </c>
+      <c r="B43" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>NorESM_RCP45_VolcConst</v>
+      </c>
+      <c r="C43" s="8">
+        <f>[3]final_combined_32methods_wide_f!C$10</f>
+        <v>0.56090986534166298</v>
+      </c>
+      <c r="D43" s="8">
+        <f>[3]final_combined_32methods_wide_f!D$10</f>
+        <v>0.88161955063888198</v>
+      </c>
+      <c r="E43" s="8">
+        <f>[3]final_combined_32methods_wide_f!E$10</f>
+        <v>0.99999974469155095</v>
+      </c>
+      <c r="F43" s="9">
+        <f>[3]final_combined_32methods_wide_f!F$10</f>
+        <v>0.41856779286222301</v>
+      </c>
+      <c r="G43" s="9">
+        <f>[3]final_combined_32methods_wide_f!G$10</f>
+        <v>0.43694253348560003</v>
+      </c>
+      <c r="H43" s="9">
+        <f>[3]final_combined_32methods_wide_f!H$10</f>
+        <v>1.0166666666666599</v>
+      </c>
+      <c r="I43" s="10">
+        <f>[3]final_combined_32methods_wide_f!I$10</f>
+        <v>2.9465985614831301E-2</v>
+      </c>
+      <c r="J43" s="10">
+        <f>[3]final_combined_32methods_wide_f!J$10</f>
+        <v>2.8759257707692599E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
 </file>